--- a/outputs/daily/hr_rankings_2026-08-25.xlsx
+++ b/outputs/daily/hr_rankings_2026-08-25.xlsx
@@ -10090,34 +10090,30 @@
       </c>
       <c r="W35" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X35" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z35" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X35" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="Y35" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z35" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA35" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB35" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed</t>
-        </is>
-      </c>
+      <c r="AB35" t="inlineStr"/>
       <c r="AC35" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -17070,34 +17066,30 @@
       </c>
       <c r="W60" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X60" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="Y60" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z60" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X60" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="Y60" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z60" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA60" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB60" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed</t>
-        </is>
-      </c>
+      <c r="AB60" t="inlineStr"/>
       <c r="AC60" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -22402,34 +22394,30 @@
       </c>
       <c r="W79" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X79" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Y79" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z79" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X79" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="Y79" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z79" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA79" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB79" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed</t>
-        </is>
-      </c>
+      <c r="AB79" t="inlineStr"/>
       <c r="AC79" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -27166,34 +27154,30 @@
       </c>
       <c r="W96" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X96" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="Y96" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z96" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X96" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="Y96" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z96" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA96" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB96" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed</t>
-        </is>
-      </c>
+      <c r="AB96" t="inlineStr"/>
       <c r="AC96" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -49214,34 +49198,30 @@
       </c>
       <c r="W175" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X175" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="Y175" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z175" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X175" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="Y175" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z175" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA175" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB175" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed</t>
-        </is>
-      </c>
+      <c r="AB175" t="inlineStr"/>
       <c r="AC175" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -57870,7 +57850,7 @@
       </c>
       <c r="W206" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="X206" t="inlineStr">
@@ -57895,7 +57875,7 @@
       </c>
       <c r="AB206" t="inlineStr">
         <is>
-          <t>RotoWire not confirmed; order MLB 6 vs RotoWire 9</t>
+          <t>order MLB 6 vs RotoWire 9</t>
         </is>
       </c>
       <c r="AC206" t="inlineStr">
@@ -62918,7 +62898,7 @@
       </c>
       <c r="W224" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="X224" t="inlineStr">
@@ -62943,7 +62923,7 @@
       </c>
       <c r="AB224" t="inlineStr">
         <is>
-          <t>RotoWire not confirmed; order MLB 7 vs RotoWire 6</t>
+          <t>order MLB 7 vs RotoWire 6</t>
         </is>
       </c>
       <c r="AC224" t="inlineStr">
@@ -63202,34 +63182,30 @@
       </c>
       <c r="W225" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X225" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="Y225" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z225" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X225" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="Y225" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z225" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA225" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB225" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed</t>
-        </is>
-      </c>
+      <c r="AB225" t="inlineStr"/>
       <c r="AC225" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>

--- a/outputs/daily/hr_rankings_2026-08-25.xlsx
+++ b/outputs/daily/hr_rankings_2026-08-25.xlsx
@@ -1344,7 +1344,7 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>67.2</v>
+        <v>67</v>
       </c>
       <c r="M4" t="inlineStr">
         <is>
@@ -1368,7 +1368,7 @@
         <v>50.2</v>
       </c>
       <c r="R4" t="n">
-        <v>42.1</v>
+        <v>40.6</v>
       </c>
       <c r="S4" t="n">
         <v>100</v>
@@ -1559,7 +1559,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>77</t>
+          <t>78</t>
         </is>
       </c>
       <c r="BI4" t="inlineStr">
@@ -5824,7 +5824,7 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>57.6</v>
+        <v>57.4</v>
       </c>
       <c r="M20" t="inlineStr">
         <is>
@@ -5848,7 +5848,7 @@
         <v>38.5</v>
       </c>
       <c r="R20" t="n">
-        <v>42.1</v>
+        <v>40.6</v>
       </c>
       <c r="S20" t="n">
         <v>100</v>
@@ -6039,7 +6039,7 @@
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>77</t>
+          <t>78</t>
         </is>
       </c>
       <c r="BI20" t="inlineStr">
@@ -6104,7 +6104,7 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>57.6</v>
+        <v>57.3</v>
       </c>
       <c r="M21" t="inlineStr">
         <is>
@@ -6128,7 +6128,7 @@
         <v>50.2</v>
       </c>
       <c r="R21" t="n">
-        <v>42.1</v>
+        <v>40.6</v>
       </c>
       <c r="S21" t="n">
         <v>96.59999999999999</v>
@@ -6319,7 +6319,7 @@
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>77</t>
+          <t>78</t>
         </is>
       </c>
       <c r="BI21" t="inlineStr">
@@ -8015,47 +8015,47 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>695657</t>
+          <t>668227</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Colson Montgomery</t>
+          <t>Randy Arozarena</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>CWS</t>
+          <t>SEA</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>TEX</t>
+          <t>PHI</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>2026-08-25T23:40:00Z</t>
+          <t>2026-08-26T01:40:00Z</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Warmup</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>Jacob deGrom</t>
+          <t>Aaron Nola</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>594798</t>
+          <t>605400</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
@@ -8078,26 +8078,26 @@
       </c>
       <c r="O28" t="inlineStr">
         <is>
-          <t>Strong Barrel, Platoon Edge</t>
+          <t>Premium Lineup Spot, Hot Hitter/Streak</t>
         </is>
       </c>
       <c r="P28" t="n">
-        <v>52</v>
+        <v>39.7</v>
       </c>
       <c r="Q28" t="n">
-        <v>50.2</v>
+        <v>49.1</v>
       </c>
       <c r="R28" t="n">
-        <v>42.1</v>
+        <v>68.40000000000001</v>
       </c>
       <c r="S28" t="n">
-        <v>86.40000000000001</v>
+        <v>93.2</v>
       </c>
       <c r="T28" t="n">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="U28" t="n">
-        <v>29.2</v>
+        <v>71.59999999999999</v>
       </c>
       <c r="V28" t="inlineStr">
         <is>
@@ -8111,7 +8111,7 @@
       </c>
       <c r="X28" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="Y28" t="inlineStr">
@@ -8149,7 +8149,7 @@
       </c>
       <c r="AH28" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AI28" t="inlineStr">
@@ -8159,17 +8159,17 @@
       </c>
       <c r="AJ28" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AK28" t="inlineStr">
         <is>
-          <t>Last 7 games: 5/26, 1 HR</t>
+          <t>Hot streak: 3 HR in last 7 games</t>
         </is>
       </c>
       <c r="AL28" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 8.9% barrel, 19.7 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 9.4% barrel, 27.1 HR allowed</t>
         </is>
       </c>
       <c r="AM28" t="inlineStr">
@@ -8179,112 +8179,112 @@
       </c>
       <c r="AN28" t="inlineStr">
         <is>
-          <t>13.03</t>
+          <t>8.84</t>
         </is>
       </c>
       <c r="AO28" t="inlineStr">
         <is>
-          <t>42.61</t>
+          <t>44.86</t>
         </is>
       </c>
       <c r="AP28" t="inlineStr">
         <is>
-          <t>89.05</t>
+          <t>90.95</t>
         </is>
       </c>
       <c r="AQ28" t="inlineStr">
         <is>
-          <t>101.8037</t>
+          <t>101.0657</t>
         </is>
       </c>
       <c r="AR28" t="inlineStr">
         <is>
-          <t>0.4366</t>
+          <t>0.4198</t>
         </is>
       </c>
       <c r="AS28" t="inlineStr">
         <is>
-          <t>0.2227</t>
+          <t>0.1683</t>
         </is>
       </c>
       <c r="AT28" t="inlineStr">
         <is>
-          <t>0.313</t>
+          <t>0.3431</t>
         </is>
       </c>
       <c r="AU28" t="inlineStr">
         <is>
-          <t>76.65</t>
+          <t>71.32</t>
         </is>
       </c>
       <c r="AV28" t="inlineStr">
         <is>
-          <t>69.67</t>
+          <t>24.59</t>
         </is>
       </c>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>49.23</t>
+          <t>33.77</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>34.0</t>
+          <t>24.31</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr">
         <is>
-          <t>25.2</t>
+          <t>22.1</t>
         </is>
       </c>
       <c r="AZ28" t="inlineStr">
         <is>
-          <t>0.2375</t>
+          <t>0.1901</t>
         </is>
       </c>
       <c r="BA28" t="inlineStr">
         <is>
-          <t>8.95</t>
+          <t>9.38</t>
         </is>
       </c>
       <c r="BB28" t="inlineStr">
         <is>
-          <t>44.7</t>
+          <t>42.39</t>
         </is>
       </c>
       <c r="BC28" t="inlineStr">
         <is>
-          <t>90.52</t>
+          <t>88.98</t>
         </is>
       </c>
       <c r="BD28" t="inlineStr">
         <is>
-          <t>0.3945</t>
+          <t>0.4191</t>
         </is>
       </c>
       <c r="BE28" t="inlineStr">
         <is>
-          <t>0.1644</t>
+          <t>0.1738</t>
         </is>
       </c>
       <c r="BF28" t="inlineStr">
         <is>
-          <t>29.74</t>
+          <t>27.46</t>
         </is>
       </c>
       <c r="BG28" t="inlineStr">
         <is>
-          <t>In From CF</t>
+          <t>Out To CF</t>
         </is>
       </c>
       <c r="BH28" t="inlineStr">
         <is>
-          <t>77</t>
+          <t>84</t>
         </is>
       </c>
       <c r="BI28" t="inlineStr">
         <is>
-          <t>Rate Field</t>
+          <t>T-Mobile Park</t>
         </is>
       </c>
       <c r="BJ28" t="inlineStr"/>
@@ -8295,47 +8295,47 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>668227</t>
+          <t>695657</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Randy Arozarena</t>
+          <t>Colson Montgomery</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>SEA</t>
+          <t>CWS</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>PHI</t>
+          <t>TEX</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>2026-08-26T01:40:00Z</t>
+          <t>2026-08-25T23:40:00Z</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>Aaron Nola</t>
+          <t>Jacob deGrom</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>605400</t>
+          <t>594798</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
@@ -8344,7 +8344,7 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>56.3</v>
+        <v>56</v>
       </c>
       <c r="M29" t="inlineStr">
         <is>
@@ -8358,26 +8358,26 @@
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>Premium Lineup Spot, Hot Hitter/Streak</t>
+          <t>Strong Barrel, Platoon Edge</t>
         </is>
       </c>
       <c r="P29" t="n">
-        <v>39.7</v>
+        <v>52</v>
       </c>
       <c r="Q29" t="n">
-        <v>49.1</v>
+        <v>50.2</v>
       </c>
       <c r="R29" t="n">
-        <v>68.40000000000001</v>
+        <v>40.6</v>
       </c>
       <c r="S29" t="n">
-        <v>93.2</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="T29" t="n">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="U29" t="n">
-        <v>71.59999999999999</v>
+        <v>29.2</v>
       </c>
       <c r="V29" t="inlineStr">
         <is>
@@ -8391,7 +8391,7 @@
       </c>
       <c r="X29" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="Y29" t="inlineStr">
@@ -8429,7 +8429,7 @@
       </c>
       <c r="AH29" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AI29" t="inlineStr">
@@ -8439,17 +8439,17 @@
       </c>
       <c r="AJ29" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AK29" t="inlineStr">
         <is>
-          <t>Hot streak: 3 HR in last 7 games</t>
+          <t>Last 7 games: 5/26, 1 HR</t>
         </is>
       </c>
       <c r="AL29" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 9.4% barrel, 27.1 HR allowed</t>
+          <t>platoon edge; pitcher baseline 8.9% barrel, 19.7 HR allowed</t>
         </is>
       </c>
       <c r="AM29" t="inlineStr">
@@ -8459,112 +8459,112 @@
       </c>
       <c r="AN29" t="inlineStr">
         <is>
-          <t>8.84</t>
+          <t>13.03</t>
         </is>
       </c>
       <c r="AO29" t="inlineStr">
         <is>
-          <t>44.86</t>
+          <t>42.61</t>
         </is>
       </c>
       <c r="AP29" t="inlineStr">
         <is>
-          <t>90.95</t>
+          <t>89.05</t>
         </is>
       </c>
       <c r="AQ29" t="inlineStr">
         <is>
-          <t>101.0657</t>
+          <t>101.8037</t>
         </is>
       </c>
       <c r="AR29" t="inlineStr">
         <is>
-          <t>0.4198</t>
+          <t>0.4366</t>
         </is>
       </c>
       <c r="AS29" t="inlineStr">
         <is>
-          <t>0.1683</t>
+          <t>0.2227</t>
         </is>
       </c>
       <c r="AT29" t="inlineStr">
         <is>
-          <t>0.3431</t>
+          <t>0.313</t>
         </is>
       </c>
       <c r="AU29" t="inlineStr">
         <is>
-          <t>71.32</t>
+          <t>76.65</t>
         </is>
       </c>
       <c r="AV29" t="inlineStr">
         <is>
-          <t>24.59</t>
+          <t>69.67</t>
         </is>
       </c>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>33.77</t>
+          <t>49.23</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>24.31</t>
+          <t>34.0</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr">
         <is>
-          <t>22.1</t>
+          <t>25.2</t>
         </is>
       </c>
       <c r="AZ29" t="inlineStr">
         <is>
-          <t>0.1901</t>
+          <t>0.2375</t>
         </is>
       </c>
       <c r="BA29" t="inlineStr">
         <is>
-          <t>9.38</t>
+          <t>8.95</t>
         </is>
       </c>
       <c r="BB29" t="inlineStr">
         <is>
-          <t>42.39</t>
+          <t>44.7</t>
         </is>
       </c>
       <c r="BC29" t="inlineStr">
         <is>
-          <t>88.98</t>
+          <t>90.52</t>
         </is>
       </c>
       <c r="BD29" t="inlineStr">
         <is>
-          <t>0.4191</t>
+          <t>0.3945</t>
         </is>
       </c>
       <c r="BE29" t="inlineStr">
         <is>
-          <t>0.1738</t>
+          <t>0.1644</t>
         </is>
       </c>
       <c r="BF29" t="inlineStr">
         <is>
-          <t>27.46</t>
+          <t>29.74</t>
         </is>
       </c>
       <c r="BG29" t="inlineStr">
         <is>
-          <t>Out To CF</t>
+          <t>In From CF</t>
         </is>
       </c>
       <c r="BH29" t="inlineStr">
         <is>
-          <t>84</t>
+          <t>78</t>
         </is>
       </c>
       <c r="BI29" t="inlineStr">
         <is>
-          <t>T-Mobile Park</t>
+          <t>Rate Field</t>
         </is>
       </c>
       <c r="BJ29" t="inlineStr"/>
@@ -13660,7 +13660,7 @@
         </is>
       </c>
       <c r="L48" t="n">
-        <v>52.3</v>
+        <v>52.1</v>
       </c>
       <c r="M48" t="inlineStr">
         <is>
@@ -13684,7 +13684,7 @@
         <v>38.5</v>
       </c>
       <c r="R48" t="n">
-        <v>42.1</v>
+        <v>40.6</v>
       </c>
       <c r="S48" t="n">
         <v>76.2</v>
@@ -13875,7 +13875,7 @@
       </c>
       <c r="BH48" t="inlineStr">
         <is>
-          <t>77</t>
+          <t>78</t>
         </is>
       </c>
       <c r="BI48" t="inlineStr">
@@ -15011,56 +15011,56 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>694671</t>
+          <t>687093</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Wyatt Langford</t>
+          <t>Vaughn Grissom</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>TEX</t>
+          <t>LAA</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>CWS</t>
+          <t>CLE</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>2026-08-25T23:40:00Z</t>
+          <t>2026-08-26T01:38:00Z</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Warmup</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>Anthony Kay</t>
+          <t>Gavin Williams</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>641743</t>
+          <t>668909</t>
         </is>
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>R</t>
         </is>
       </c>
       <c r="L53" t="n">
-        <v>51.1</v>
+        <v>51</v>
       </c>
       <c r="M53" t="inlineStr">
         <is>
@@ -15074,26 +15074,26 @@
       </c>
       <c r="O53" t="inlineStr">
         <is>
-          <t>Premium Lineup Spot, Platoon Edge</t>
+          <t>Good Environment, Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P53" t="n">
-        <v>39.8</v>
+        <v>24.8</v>
       </c>
       <c r="Q53" t="n">
-        <v>38.5</v>
+        <v>56.2</v>
       </c>
       <c r="R53" t="n">
-        <v>42.1</v>
+        <v>71.2</v>
       </c>
       <c r="S53" t="n">
-        <v>96.59999999999999</v>
+        <v>94.90000000000001</v>
       </c>
       <c r="T53" t="n">
-        <v>78</v>
+        <v>50</v>
       </c>
       <c r="U53" t="n">
-        <v>37.8</v>
+        <v>16.6</v>
       </c>
       <c r="V53" t="inlineStr">
         <is>
@@ -15107,7 +15107,7 @@
       </c>
       <c r="X53" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="Y53" t="inlineStr">
@@ -15128,7 +15128,7 @@
       <c r="AB53" t="inlineStr"/>
       <c r="AC53" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026</t>
+          <t>H:2026 P:2026/2025</t>
         </is>
       </c>
       <c r="AD53" t="inlineStr"/>
@@ -15145,27 +15145,27 @@
       </c>
       <c r="AH53" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AI53" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>26</t>
         </is>
       </c>
       <c r="AJ53" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK53" t="inlineStr">
         <is>
-          <t>Last 7 games: 7/28, 1 HR</t>
+          <t>Last 7 games: 6/26, 0 HR</t>
         </is>
       </c>
       <c r="AL53" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 8.2% barrel, 16.0 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 10.9% barrel, 24.4 HR allowed</t>
         </is>
       </c>
       <c r="AM53" t="inlineStr">
@@ -15175,112 +15175,112 @@
       </c>
       <c r="AN53" t="inlineStr">
         <is>
-          <t>9.24</t>
+          <t>6.4</t>
         </is>
       </c>
       <c r="AO53" t="inlineStr">
         <is>
-          <t>42.31</t>
+          <t>37.5</t>
         </is>
       </c>
       <c r="AP53" t="inlineStr">
         <is>
-          <t>90.0</t>
+          <t>87.8</t>
         </is>
       </c>
       <c r="AQ53" t="inlineStr">
         <is>
-          <t>100.9419</t>
+          <t>99.0516</t>
         </is>
       </c>
       <c r="AR53" t="inlineStr">
         <is>
-          <t>0.4137</t>
+          <t>0.377</t>
         </is>
       </c>
       <c r="AS53" t="inlineStr">
         <is>
-          <t>0.1736</t>
+          <t>0.127</t>
         </is>
       </c>
       <c r="AT53" t="inlineStr">
         <is>
-          <t>0.3222</t>
+          <t>0.309</t>
         </is>
       </c>
       <c r="AU53" t="inlineStr">
         <is>
-          <t>72.68</t>
+          <t>71.3</t>
         </is>
       </c>
       <c r="AV53" t="inlineStr">
         <is>
-          <t>25.54</t>
+          <t>18.4</t>
         </is>
       </c>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>43.38</t>
+          <t>41.4</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>28.64</t>
+          <t>25.1</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr">
         <is>
-          <t>17.1</t>
+          <t>7.0</t>
         </is>
       </c>
       <c r="AZ53" t="inlineStr">
         <is>
-          <t>0.2033</t>
+          <t>0.126</t>
         </is>
       </c>
       <c r="BA53" t="inlineStr">
         <is>
-          <t>8.2</t>
+          <t>10.89</t>
         </is>
       </c>
       <c r="BB53" t="inlineStr">
         <is>
-          <t>39.7</t>
+          <t>46.68</t>
         </is>
       </c>
       <c r="BC53" t="inlineStr">
         <is>
-          <t>88.4</t>
+          <t>90.26</t>
         </is>
       </c>
       <c r="BD53" t="inlineStr">
         <is>
-          <t>0.404</t>
+          <t>0.4071</t>
         </is>
       </c>
       <c r="BE53" t="inlineStr">
         <is>
-          <t>0.144</t>
+          <t>0.1789</t>
         </is>
       </c>
       <c r="BF53" t="inlineStr">
         <is>
-          <t>21.8</t>
+          <t>25.86</t>
         </is>
       </c>
       <c r="BG53" t="inlineStr">
         <is>
-          <t>In From CF</t>
+          <t>Out To CF</t>
         </is>
       </c>
       <c r="BH53" t="inlineStr">
         <is>
-          <t>77</t>
+          <t>90</t>
         </is>
       </c>
       <c r="BI53" t="inlineStr">
         <is>
-          <t>Rate Field</t>
+          <t>Angel Stadium</t>
         </is>
       </c>
       <c r="BJ53" t="inlineStr"/>
@@ -15291,56 +15291,56 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>687093</t>
+          <t>694671</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Vaughn Grissom</t>
+          <t>Wyatt Langford</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>LAA</t>
+          <t>TEX</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>CLE</t>
+          <t>CWS</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>2026-08-26T01:38:00Z</t>
+          <t>2026-08-25T23:40:00Z</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>Gavin Williams</t>
+          <t>Anthony Kay</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>668909</t>
+          <t>641743</t>
         </is>
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>L</t>
         </is>
       </c>
       <c r="L54" t="n">
-        <v>51</v>
+        <v>50.9</v>
       </c>
       <c r="M54" t="inlineStr">
         <is>
@@ -15354,26 +15354,26 @@
       </c>
       <c r="O54" t="inlineStr">
         <is>
-          <t>Good Environment, Premium Lineup Spot</t>
+          <t>Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P54" t="n">
-        <v>24.8</v>
+        <v>39.8</v>
       </c>
       <c r="Q54" t="n">
-        <v>56.2</v>
+        <v>38.5</v>
       </c>
       <c r="R54" t="n">
-        <v>71.2</v>
+        <v>40.6</v>
       </c>
       <c r="S54" t="n">
-        <v>94.90000000000001</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="T54" t="n">
-        <v>50</v>
+        <v>78</v>
       </c>
       <c r="U54" t="n">
-        <v>16.6</v>
+        <v>37.8</v>
       </c>
       <c r="V54" t="inlineStr">
         <is>
@@ -15387,7 +15387,7 @@
       </c>
       <c r="X54" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="Y54" t="inlineStr">
@@ -15408,7 +15408,7 @@
       <c r="AB54" t="inlineStr"/>
       <c r="AC54" t="inlineStr">
         <is>
-          <t>H:2026 P:2026/2025</t>
+          <t>H:2026/2025 P:2026</t>
         </is>
       </c>
       <c r="AD54" t="inlineStr"/>
@@ -15425,27 +15425,27 @@
       </c>
       <c r="AH54" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AI54" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>28</t>
         </is>
       </c>
       <c r="AJ54" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AK54" t="inlineStr">
         <is>
-          <t>Last 7 games: 6/26, 0 HR</t>
+          <t>Last 7 games: 7/28, 1 HR</t>
         </is>
       </c>
       <c r="AL54" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 10.9% barrel, 24.4 HR allowed</t>
+          <t>platoon edge; pitcher baseline 8.2% barrel, 16.0 HR allowed</t>
         </is>
       </c>
       <c r="AM54" t="inlineStr">
@@ -15455,112 +15455,112 @@
       </c>
       <c r="AN54" t="inlineStr">
         <is>
-          <t>6.4</t>
+          <t>9.24</t>
         </is>
       </c>
       <c r="AO54" t="inlineStr">
         <is>
-          <t>37.5</t>
+          <t>42.31</t>
         </is>
       </c>
       <c r="AP54" t="inlineStr">
         <is>
-          <t>87.8</t>
+          <t>90.0</t>
         </is>
       </c>
       <c r="AQ54" t="inlineStr">
         <is>
-          <t>99.0516</t>
+          <t>100.9419</t>
         </is>
       </c>
       <c r="AR54" t="inlineStr">
         <is>
-          <t>0.377</t>
+          <t>0.4137</t>
         </is>
       </c>
       <c r="AS54" t="inlineStr">
         <is>
-          <t>0.127</t>
+          <t>0.1736</t>
         </is>
       </c>
       <c r="AT54" t="inlineStr">
         <is>
-          <t>0.309</t>
+          <t>0.3222</t>
         </is>
       </c>
       <c r="AU54" t="inlineStr">
         <is>
-          <t>71.3</t>
+          <t>72.68</t>
         </is>
       </c>
       <c r="AV54" t="inlineStr">
         <is>
-          <t>18.4</t>
+          <t>25.54</t>
         </is>
       </c>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>41.4</t>
+          <t>43.38</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>25.1</t>
+          <t>28.64</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr">
         <is>
-          <t>7.0</t>
+          <t>17.1</t>
         </is>
       </c>
       <c r="AZ54" t="inlineStr">
         <is>
-          <t>0.126</t>
+          <t>0.2033</t>
         </is>
       </c>
       <c r="BA54" t="inlineStr">
         <is>
-          <t>10.89</t>
+          <t>8.2</t>
         </is>
       </c>
       <c r="BB54" t="inlineStr">
         <is>
-          <t>46.68</t>
+          <t>39.7</t>
         </is>
       </c>
       <c r="BC54" t="inlineStr">
         <is>
-          <t>90.26</t>
+          <t>88.4</t>
         </is>
       </c>
       <c r="BD54" t="inlineStr">
         <is>
-          <t>0.4071</t>
+          <t>0.404</t>
         </is>
       </c>
       <c r="BE54" t="inlineStr">
         <is>
-          <t>0.1789</t>
+          <t>0.144</t>
         </is>
       </c>
       <c r="BF54" t="inlineStr">
         <is>
-          <t>25.86</t>
+          <t>21.8</t>
         </is>
       </c>
       <c r="BG54" t="inlineStr">
         <is>
-          <t>Out To CF</t>
+          <t>In From CF</t>
         </is>
       </c>
       <c r="BH54" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>78</t>
         </is>
       </c>
       <c r="BI54" t="inlineStr">
         <is>
-          <t>Angel Stadium</t>
+          <t>Rate Field</t>
         </is>
       </c>
       <c r="BJ54" t="inlineStr"/>
@@ -16127,52 +16127,52 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>679822</t>
+          <t>664034</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Justin Foscue</t>
+          <t>Ty France</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>TEX</t>
+          <t>SD</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>CWS</t>
+          <t>PIT</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>2026-08-25T23:40:00Z</t>
+          <t>2026-08-26T01:40:00Z</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Warmup</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>Anthony Kay</t>
+          <t>Paul Skenes</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>641743</t>
+          <t>694973</t>
         </is>
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>R</t>
         </is>
       </c>
       <c r="L57" t="n">
@@ -16190,26 +16190,26 @@
       </c>
       <c r="O57" t="inlineStr">
         <is>
-          <t>Premium Lineup Spot, Platoon Edge</t>
+          <t>Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P57" t="n">
-        <v>38.6</v>
+        <v>43.5</v>
       </c>
       <c r="Q57" t="n">
-        <v>38.5</v>
+        <v>30.1</v>
       </c>
       <c r="R57" t="n">
-        <v>42.1</v>
+        <v>59.6</v>
       </c>
       <c r="S57" t="n">
-        <v>93.2</v>
+        <v>94.90000000000001</v>
       </c>
       <c r="T57" t="n">
-        <v>78</v>
+        <v>50</v>
       </c>
       <c r="U57" t="n">
-        <v>37.8</v>
+        <v>39.5</v>
       </c>
       <c r="V57" t="inlineStr">
         <is>
@@ -16223,7 +16223,7 @@
       </c>
       <c r="X57" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="Y57" t="inlineStr">
@@ -16244,7 +16244,7 @@
       <c r="AB57" t="inlineStr"/>
       <c r="AC57" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD57" t="inlineStr"/>
@@ -16261,12 +16261,12 @@
       </c>
       <c r="AH57" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AI57" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>23</t>
         </is>
       </c>
       <c r="AJ57" t="inlineStr">
@@ -16276,127 +16276,127 @@
       </c>
       <c r="AK57" t="inlineStr">
         <is>
-          <t>Last 7 games: 5/20, 1 HR</t>
+          <t>Last 7 games: 6/23, 1 HR</t>
         </is>
       </c>
       <c r="AL57" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 8.2% barrel, 16.0 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 6.9% barrel, 13.1 HR allowed</t>
         </is>
       </c>
       <c r="AM57" t="inlineStr">
         <is>
-          <t>fly-ball profile; pitcher fly-ball pressure modest</t>
+          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN57" t="inlineStr">
         <is>
-          <t>6.93</t>
+          <t>9.31</t>
         </is>
       </c>
       <c r="AO57" t="inlineStr">
         <is>
-          <t>48.92</t>
+          <t>47.56</t>
         </is>
       </c>
       <c r="AP57" t="inlineStr">
         <is>
-          <t>90.2</t>
+          <t>91.32</t>
         </is>
       </c>
       <c r="AQ57" t="inlineStr">
         <is>
-          <t>99.4562</t>
+          <t>101.1459</t>
         </is>
       </c>
       <c r="AR57" t="inlineStr">
         <is>
-          <t>0.3839</t>
+          <t>0.4313</t>
         </is>
       </c>
       <c r="AS57" t="inlineStr">
         <is>
-          <t>0.1677</t>
+          <t>0.1779</t>
         </is>
       </c>
       <c r="AT57" t="inlineStr">
         <is>
-          <t>0.282</t>
+          <t>0.3308</t>
         </is>
       </c>
       <c r="AU57" t="inlineStr">
         <is>
-          <t>71.1</t>
+          <t>71.77</t>
         </is>
       </c>
       <c r="AV57" t="inlineStr">
         <is>
-          <t>10.22</t>
+          <t>19.39</t>
         </is>
       </c>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>47.97</t>
+          <t>36.57</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>35.23</t>
+          <t>25.53</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr">
         <is>
-          <t>5.6</t>
+          <t>14.7</t>
         </is>
       </c>
       <c r="AZ57" t="inlineStr">
         <is>
-          <t>0.181</t>
+          <t>0.1856</t>
         </is>
       </c>
       <c r="BA57" t="inlineStr">
         <is>
-          <t>8.2</t>
+          <t>6.92</t>
         </is>
       </c>
       <c r="BB57" t="inlineStr">
         <is>
-          <t>39.7</t>
+          <t>39.33</t>
         </is>
       </c>
       <c r="BC57" t="inlineStr">
         <is>
-          <t>88.4</t>
+          <t>88.23</t>
         </is>
       </c>
       <c r="BD57" t="inlineStr">
         <is>
-          <t>0.404</t>
+          <t>0.335</t>
         </is>
       </c>
       <c r="BE57" t="inlineStr">
         <is>
-          <t>0.144</t>
+          <t>0.1253</t>
         </is>
       </c>
       <c r="BF57" t="inlineStr">
         <is>
-          <t>21.8</t>
+          <t>23.99</t>
         </is>
       </c>
       <c r="BG57" t="inlineStr">
         <is>
-          <t>In From CF</t>
+          <t>Out To RF</t>
         </is>
       </c>
       <c r="BH57" t="inlineStr">
         <is>
-          <t>77</t>
+          <t>80</t>
         </is>
       </c>
       <c r="BI57" t="inlineStr">
         <is>
-          <t>Rate Field</t>
+          <t>Petco Park</t>
         </is>
       </c>
       <c r="BJ57" t="inlineStr"/>
@@ -16407,22 +16407,22 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>664034</t>
+          <t>669016</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Ty France</t>
+          <t>Brandon Marsh</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>SD</t>
+          <t>PHI</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>PIT</t>
+          <t>SEA</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -16437,17 +16437,17 @@
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>7</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>Paul Skenes</t>
+          <t>George Kirby</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>694973</t>
+          <t>669923</t>
         </is>
       </c>
       <c r="K58" t="inlineStr">
@@ -16456,7 +16456,7 @@
         </is>
       </c>
       <c r="L58" t="n">
-        <v>50.3</v>
+        <v>50.1</v>
       </c>
       <c r="M58" t="inlineStr">
         <is>
@@ -16470,26 +16470,26 @@
       </c>
       <c r="O58" t="inlineStr">
         <is>
-          <t>Premium Lineup Spot</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P58" t="n">
-        <v>43.5</v>
+        <v>38</v>
       </c>
       <c r="Q58" t="n">
-        <v>30.1</v>
+        <v>41.5</v>
       </c>
       <c r="R58" t="n">
-        <v>59.6</v>
+        <v>68.40000000000001</v>
       </c>
       <c r="S58" t="n">
-        <v>94.90000000000001</v>
+        <v>64.3</v>
       </c>
       <c r="T58" t="n">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="U58" t="n">
-        <v>39.5</v>
+        <v>22.9</v>
       </c>
       <c r="V58" t="inlineStr">
         <is>
@@ -16503,7 +16503,7 @@
       </c>
       <c r="X58" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>7</t>
         </is>
       </c>
       <c r="Y58" t="inlineStr">
@@ -16546,22 +16546,22 @@
       </c>
       <c r="AI58" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>22</t>
         </is>
       </c>
       <c r="AJ58" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK58" t="inlineStr">
         <is>
-          <t>Last 7 games: 6/23, 1 HR</t>
+          <t>Last 7 games: 6/22, 0 HR</t>
         </is>
       </c>
       <c r="AL58" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 6.9% barrel, 13.1 HR allowed</t>
+          <t>platoon edge; pitcher baseline 7.4% barrel, 16.4 HR allowed</t>
         </is>
       </c>
       <c r="AM58" t="inlineStr">
@@ -16571,112 +16571,112 @@
       </c>
       <c r="AN58" t="inlineStr">
         <is>
-          <t>9.31</t>
+          <t>8.54</t>
         </is>
       </c>
       <c r="AO58" t="inlineStr">
         <is>
-          <t>47.56</t>
+          <t>45.0</t>
         </is>
       </c>
       <c r="AP58" t="inlineStr">
         <is>
-          <t>91.32</t>
+          <t>89.91</t>
         </is>
       </c>
       <c r="AQ58" t="inlineStr">
         <is>
-          <t>101.1459</t>
+          <t>100.2023</t>
         </is>
       </c>
       <c r="AR58" t="inlineStr">
         <is>
-          <t>0.4313</t>
+          <t>0.4208</t>
         </is>
       </c>
       <c r="AS58" t="inlineStr">
         <is>
-          <t>0.1779</t>
+          <t>0.1606</t>
         </is>
       </c>
       <c r="AT58" t="inlineStr">
         <is>
-          <t>0.3308</t>
+          <t>0.316</t>
         </is>
       </c>
       <c r="AU58" t="inlineStr">
         <is>
-          <t>71.77</t>
+          <t>71.54</t>
         </is>
       </c>
       <c r="AV58" t="inlineStr">
         <is>
-          <t>19.39</t>
+          <t>15.79</t>
         </is>
       </c>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>36.57</t>
+          <t>37.63</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>25.53</t>
+          <t>26.45</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr">
         <is>
-          <t>14.7</t>
+          <t>15.2</t>
         </is>
       </c>
       <c r="AZ58" t="inlineStr">
         <is>
-          <t>0.1856</t>
+          <t>0.1609</t>
         </is>
       </c>
       <c r="BA58" t="inlineStr">
         <is>
-          <t>6.92</t>
+          <t>7.41</t>
         </is>
       </c>
       <c r="BB58" t="inlineStr">
         <is>
-          <t>39.33</t>
+          <t>42.85</t>
         </is>
       </c>
       <c r="BC58" t="inlineStr">
         <is>
-          <t>88.23</t>
+          <t>90.04</t>
         </is>
       </c>
       <c r="BD58" t="inlineStr">
         <is>
-          <t>0.335</t>
+          <t>0.4025</t>
         </is>
       </c>
       <c r="BE58" t="inlineStr">
         <is>
-          <t>0.1253</t>
+          <t>0.1451</t>
         </is>
       </c>
       <c r="BF58" t="inlineStr">
         <is>
-          <t>23.99</t>
+          <t>24.73</t>
         </is>
       </c>
       <c r="BG58" t="inlineStr">
         <is>
-          <t>Out To RF</t>
+          <t>Out To CF</t>
         </is>
       </c>
       <c r="BH58" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>84</t>
         </is>
       </c>
       <c r="BI58" t="inlineStr">
         <is>
-          <t>Petco Park</t>
+          <t>T-Mobile Park</t>
         </is>
       </c>
       <c r="BJ58" t="inlineStr"/>
@@ -16687,56 +16687,56 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>669016</t>
+          <t>679822</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Brandon Marsh</t>
+          <t>Justin Foscue</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>PHI</t>
+          <t>TEX</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>SEA</t>
+          <t>CWS</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>2026-08-26T01:40:00Z</t>
+          <t>2026-08-25T23:40:00Z</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>George Kirby</t>
+          <t>Anthony Kay</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>669923</t>
+          <t>641743</t>
         </is>
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>L</t>
         </is>
       </c>
       <c r="L59" t="n">
-        <v>50.1</v>
+        <v>50</v>
       </c>
       <c r="M59" t="inlineStr">
         <is>
@@ -16750,26 +16750,26 @@
       </c>
       <c r="O59" t="inlineStr">
         <is>
-          <t>Platoon Edge</t>
+          <t>Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P59" t="n">
-        <v>38</v>
+        <v>38.6</v>
       </c>
       <c r="Q59" t="n">
-        <v>41.5</v>
+        <v>38.5</v>
       </c>
       <c r="R59" t="n">
-        <v>68.40000000000001</v>
+        <v>40.6</v>
       </c>
       <c r="S59" t="n">
-        <v>64.3</v>
+        <v>93.2</v>
       </c>
       <c r="T59" t="n">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="U59" t="n">
-        <v>22.9</v>
+        <v>37.8</v>
       </c>
       <c r="V59" t="inlineStr">
         <is>
@@ -16783,7 +16783,7 @@
       </c>
       <c r="X59" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>1</t>
         </is>
       </c>
       <c r="Y59" t="inlineStr">
@@ -16804,7 +16804,7 @@
       <c r="AB59" t="inlineStr"/>
       <c r="AC59" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026/2025</t>
+          <t>H:2026/2025 P:2026</t>
         </is>
       </c>
       <c r="AD59" t="inlineStr"/>
@@ -16821,142 +16821,142 @@
       </c>
       <c r="AH59" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AI59" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>20</t>
         </is>
       </c>
       <c r="AJ59" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AK59" t="inlineStr">
         <is>
-          <t>Last 7 games: 6/22, 0 HR</t>
+          <t>Last 7 games: 5/20, 1 HR</t>
         </is>
       </c>
       <c r="AL59" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 7.4% barrel, 16.4 HR allowed</t>
+          <t>platoon edge; pitcher baseline 8.2% barrel, 16.0 HR allowed</t>
         </is>
       </c>
       <c r="AM59" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
+          <t>fly-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN59" t="inlineStr">
         <is>
-          <t>8.54</t>
+          <t>6.93</t>
         </is>
       </c>
       <c r="AO59" t="inlineStr">
         <is>
-          <t>45.0</t>
+          <t>48.92</t>
         </is>
       </c>
       <c r="AP59" t="inlineStr">
         <is>
-          <t>89.91</t>
+          <t>90.2</t>
         </is>
       </c>
       <c r="AQ59" t="inlineStr">
         <is>
-          <t>100.2023</t>
+          <t>99.4562</t>
         </is>
       </c>
       <c r="AR59" t="inlineStr">
         <is>
-          <t>0.4208</t>
+          <t>0.3839</t>
         </is>
       </c>
       <c r="AS59" t="inlineStr">
         <is>
-          <t>0.1606</t>
+          <t>0.1677</t>
         </is>
       </c>
       <c r="AT59" t="inlineStr">
         <is>
-          <t>0.316</t>
+          <t>0.282</t>
         </is>
       </c>
       <c r="AU59" t="inlineStr">
         <is>
-          <t>71.54</t>
+          <t>71.1</t>
         </is>
       </c>
       <c r="AV59" t="inlineStr">
         <is>
-          <t>15.79</t>
+          <t>10.22</t>
         </is>
       </c>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>37.63</t>
+          <t>47.97</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>26.45</t>
+          <t>35.23</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr">
         <is>
-          <t>15.2</t>
+          <t>5.6</t>
         </is>
       </c>
       <c r="AZ59" t="inlineStr">
         <is>
-          <t>0.1609</t>
+          <t>0.181</t>
         </is>
       </c>
       <c r="BA59" t="inlineStr">
         <is>
-          <t>7.41</t>
+          <t>8.2</t>
         </is>
       </c>
       <c r="BB59" t="inlineStr">
         <is>
-          <t>42.85</t>
+          <t>39.7</t>
         </is>
       </c>
       <c r="BC59" t="inlineStr">
         <is>
-          <t>90.04</t>
+          <t>88.4</t>
         </is>
       </c>
       <c r="BD59" t="inlineStr">
         <is>
-          <t>0.4025</t>
+          <t>0.404</t>
         </is>
       </c>
       <c r="BE59" t="inlineStr">
         <is>
-          <t>0.1451</t>
+          <t>0.144</t>
         </is>
       </c>
       <c r="BF59" t="inlineStr">
         <is>
-          <t>24.73</t>
+          <t>21.8</t>
         </is>
       </c>
       <c r="BG59" t="inlineStr">
         <is>
-          <t>Out To CF</t>
+          <t>In From CF</t>
         </is>
       </c>
       <c r="BH59" t="inlineStr">
         <is>
-          <t>84</t>
+          <t>78</t>
         </is>
       </c>
       <c r="BI59" t="inlineStr">
         <is>
-          <t>T-Mobile Park</t>
+          <t>Rate Field</t>
         </is>
       </c>
       <c r="BJ59" t="inlineStr"/>
@@ -17807,56 +17807,56 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>607043</t>
+          <t>694376</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Brandon Nimmo</t>
+          <t>Shay Whitcomb</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>TEX</t>
+          <t>SF</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>CWS</t>
+          <t>CIN</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>2026-08-25T23:40:00Z</t>
+          <t>2026-08-26T01:45:00Z</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Warmup</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>7</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>Anthony Kay</t>
+          <t>Brady Singer</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>641743</t>
+          <t>663903</t>
         </is>
       </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>R</t>
         </is>
       </c>
       <c r="L63" t="n">
-        <v>49.3</v>
+        <v>49.2</v>
       </c>
       <c r="M63" t="inlineStr">
         <is>
@@ -17870,26 +17870,26 @@
       </c>
       <c r="O63" t="inlineStr">
         <is>
-          <t>Premium Lineup Spot</t>
+          <t>Strong Barrel</t>
         </is>
       </c>
       <c r="P63" t="n">
-        <v>48.3</v>
+        <v>41.3</v>
       </c>
       <c r="Q63" t="n">
-        <v>38.5</v>
+        <v>51.7</v>
       </c>
       <c r="R63" t="n">
-        <v>42.1</v>
+        <v>55.8</v>
       </c>
       <c r="S63" t="n">
-        <v>94.90000000000001</v>
+        <v>64.3</v>
       </c>
       <c r="T63" t="n">
         <v>50</v>
       </c>
       <c r="U63" t="n">
-        <v>0</v>
+        <v>25.3</v>
       </c>
       <c r="V63" t="inlineStr">
         <is>
@@ -17903,7 +17903,7 @@
       </c>
       <c r="X63" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>7</t>
         </is>
       </c>
       <c r="Y63" t="inlineStr">
@@ -17924,7 +17924,7 @@
       <c r="AB63" t="inlineStr"/>
       <c r="AC63" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD63" t="inlineStr"/>
@@ -17946,137 +17946,137 @@
       </c>
       <c r="AI63" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>12</t>
         </is>
       </c>
       <c r="AJ63" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AK63" t="inlineStr">
         <is>
-          <t>Last 7 games: 2/27, 0 HR</t>
+          <t>Last 7 games: 2/12, 1 HR</t>
         </is>
       </c>
       <c r="AL63" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 8.2% barrel, 16.0 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 9.5% barrel, 23.2 HR allowed</t>
         </is>
       </c>
       <c r="AM63" t="inlineStr">
         <is>
-          <t>EV profile; pitcher fly-ball pressure modest</t>
+          <t>fly-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN63" t="inlineStr">
         <is>
-          <t>9.85</t>
+          <t>11.36</t>
         </is>
       </c>
       <c r="AO63" t="inlineStr">
         <is>
-          <t>50.62</t>
+          <t>35.49</t>
         </is>
       </c>
       <c r="AP63" t="inlineStr">
         <is>
-          <t>92.11</t>
+          <t>87.93</t>
         </is>
       </c>
       <c r="AQ63" t="inlineStr">
         <is>
-          <t>102.1199</t>
+          <t>97.9997</t>
         </is>
       </c>
       <c r="AR63" t="inlineStr">
         <is>
-          <t>0.4575</t>
+          <t>0.3678</t>
         </is>
       </c>
       <c r="AS63" t="inlineStr">
         <is>
-          <t>0.1852</t>
+          <t>0.2038</t>
         </is>
       </c>
       <c r="AT63" t="inlineStr">
         <is>
-          <t>0.3462</t>
+          <t>0.2337</t>
         </is>
       </c>
       <c r="AU63" t="inlineStr">
         <is>
-          <t>72.27</t>
+          <t>71.87</t>
         </is>
       </c>
       <c r="AV63" t="inlineStr">
         <is>
-          <t>27.32</t>
+          <t>16.8</t>
         </is>
       </c>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>32.54</t>
+          <t>35.44</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>25.98</t>
+          <t>45.43</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr">
         <is>
-          <t>16.6</t>
+          <t>1.7</t>
         </is>
       </c>
       <c r="AZ63" t="inlineStr">
         <is>
-          <t>0.1614</t>
+          <t>0.1899</t>
         </is>
       </c>
       <c r="BA63" t="inlineStr">
         <is>
-          <t>8.2</t>
+          <t>9.47</t>
         </is>
       </c>
       <c r="BB63" t="inlineStr">
         <is>
-          <t>39.7</t>
+          <t>40.77</t>
         </is>
       </c>
       <c r="BC63" t="inlineStr">
         <is>
-          <t>88.4</t>
+          <t>90.58</t>
         </is>
       </c>
       <c r="BD63" t="inlineStr">
         <is>
-          <t>0.404</t>
+          <t>0.4356</t>
         </is>
       </c>
       <c r="BE63" t="inlineStr">
         <is>
-          <t>0.144</t>
+          <t>0.173</t>
         </is>
       </c>
       <c r="BF63" t="inlineStr">
         <is>
-          <t>21.8</t>
+          <t>27.63</t>
         </is>
       </c>
       <c r="BG63" t="inlineStr">
         <is>
-          <t>In From CF</t>
+          <t>Out To CF</t>
         </is>
       </c>
       <c r="BH63" t="inlineStr">
         <is>
-          <t>77</t>
+          <t>65</t>
         </is>
       </c>
       <c r="BI63" t="inlineStr">
         <is>
-          <t>Rate Field</t>
+          <t>Oracle Park</t>
         </is>
       </c>
       <c r="BJ63" t="inlineStr"/>
@@ -18087,56 +18087,56 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>694376</t>
+          <t>607043</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Shay Whitcomb</t>
+          <t>Brandon Nimmo</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>SF</t>
+          <t>TEX</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>CIN</t>
+          <t>CWS</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>2026-08-26T01:45:00Z</t>
+          <t>2026-08-25T23:40:00Z</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>Brady Singer</t>
+          <t>Anthony Kay</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>663903</t>
+          <t>641743</t>
         </is>
       </c>
       <c r="K64" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>L</t>
         </is>
       </c>
       <c r="L64" t="n">
-        <v>49.2</v>
+        <v>49.1</v>
       </c>
       <c r="M64" t="inlineStr">
         <is>
@@ -18150,26 +18150,26 @@
       </c>
       <c r="O64" t="inlineStr">
         <is>
-          <t>Strong Barrel</t>
+          <t>Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P64" t="n">
-        <v>41.3</v>
+        <v>48.3</v>
       </c>
       <c r="Q64" t="n">
-        <v>51.7</v>
+        <v>38.5</v>
       </c>
       <c r="R64" t="n">
-        <v>55.8</v>
+        <v>40.6</v>
       </c>
       <c r="S64" t="n">
-        <v>64.3</v>
+        <v>94.90000000000001</v>
       </c>
       <c r="T64" t="n">
         <v>50</v>
       </c>
       <c r="U64" t="n">
-        <v>25.3</v>
+        <v>0</v>
       </c>
       <c r="V64" t="inlineStr">
         <is>
@@ -18183,7 +18183,7 @@
       </c>
       <c r="X64" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>4</t>
         </is>
       </c>
       <c r="Y64" t="inlineStr">
@@ -18204,7 +18204,7 @@
       <c r="AB64" t="inlineStr"/>
       <c r="AC64" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026/2025</t>
+          <t>H:2026/2025 P:2026</t>
         </is>
       </c>
       <c r="AD64" t="inlineStr"/>
@@ -18226,137 +18226,137 @@
       </c>
       <c r="AI64" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>27</t>
         </is>
       </c>
       <c r="AJ64" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK64" t="inlineStr">
         <is>
-          <t>Last 7 games: 2/12, 1 HR</t>
+          <t>Last 7 games: 2/27, 0 HR</t>
         </is>
       </c>
       <c r="AL64" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 9.5% barrel, 23.2 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 8.2% barrel, 16.0 HR allowed</t>
         </is>
       </c>
       <c r="AM64" t="inlineStr">
         <is>
-          <t>fly-ball profile; pitcher fly-ball pressure modest</t>
+          <t>EV profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN64" t="inlineStr">
         <is>
-          <t>11.36</t>
+          <t>9.85</t>
         </is>
       </c>
       <c r="AO64" t="inlineStr">
         <is>
-          <t>35.49</t>
+          <t>50.62</t>
         </is>
       </c>
       <c r="AP64" t="inlineStr">
         <is>
-          <t>87.93</t>
+          <t>92.11</t>
         </is>
       </c>
       <c r="AQ64" t="inlineStr">
         <is>
-          <t>97.9997</t>
+          <t>102.1199</t>
         </is>
       </c>
       <c r="AR64" t="inlineStr">
         <is>
-          <t>0.3678</t>
+          <t>0.4575</t>
         </is>
       </c>
       <c r="AS64" t="inlineStr">
         <is>
-          <t>0.2038</t>
+          <t>0.1852</t>
         </is>
       </c>
       <c r="AT64" t="inlineStr">
         <is>
-          <t>0.2337</t>
+          <t>0.3462</t>
         </is>
       </c>
       <c r="AU64" t="inlineStr">
         <is>
-          <t>71.87</t>
+          <t>72.27</t>
         </is>
       </c>
       <c r="AV64" t="inlineStr">
         <is>
-          <t>16.8</t>
+          <t>27.32</t>
         </is>
       </c>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>35.44</t>
+          <t>32.54</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>45.43</t>
+          <t>25.98</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr">
         <is>
-          <t>1.7</t>
+          <t>16.6</t>
         </is>
       </c>
       <c r="AZ64" t="inlineStr">
         <is>
-          <t>0.1899</t>
+          <t>0.1614</t>
         </is>
       </c>
       <c r="BA64" t="inlineStr">
         <is>
-          <t>9.47</t>
+          <t>8.2</t>
         </is>
       </c>
       <c r="BB64" t="inlineStr">
         <is>
-          <t>40.77</t>
+          <t>39.7</t>
         </is>
       </c>
       <c r="BC64" t="inlineStr">
         <is>
-          <t>90.58</t>
+          <t>88.4</t>
         </is>
       </c>
       <c r="BD64" t="inlineStr">
         <is>
-          <t>0.4356</t>
+          <t>0.404</t>
         </is>
       </c>
       <c r="BE64" t="inlineStr">
         <is>
-          <t>0.173</t>
+          <t>0.144</t>
         </is>
       </c>
       <c r="BF64" t="inlineStr">
         <is>
-          <t>27.63</t>
+          <t>21.8</t>
         </is>
       </c>
       <c r="BG64" t="inlineStr">
         <is>
-          <t>Out To CF</t>
+          <t>In From CF</t>
         </is>
       </c>
       <c r="BH64" t="inlineStr">
         <is>
-          <t>65</t>
+          <t>78</t>
         </is>
       </c>
       <c r="BI64" t="inlineStr">
         <is>
-          <t>Oracle Park</t>
+          <t>Rate Field</t>
         </is>
       </c>
       <c r="BJ64" t="inlineStr"/>
@@ -21727,27 +21727,27 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>695731</t>
+          <t>687637</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Braden Montgomery</t>
+          <t>Dylan Beavers</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>CWS</t>
+          <t>BAL</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>TEX</t>
+          <t>STL</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>2026-08-25T23:40:00Z</t>
+          <t>2026-08-25T23:45:00Z</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
@@ -21757,26 +21757,26 @@
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>Jacob deGrom</t>
+          <t>Matthew Liberatore</t>
         </is>
       </c>
       <c r="J77" t="inlineStr">
         <is>
-          <t>594798</t>
+          <t>669461</t>
         </is>
       </c>
       <c r="K77" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>L</t>
         </is>
       </c>
       <c r="L77" t="n">
-        <v>46.9</v>
+        <v>46.8</v>
       </c>
       <c r="M77" t="inlineStr">
         <is>
@@ -21790,26 +21790,26 @@
       </c>
       <c r="O77" t="inlineStr">
         <is>
-          <t>Premium Lineup Spot, Platoon Edge</t>
+          <t>Hot Hitter/Streak</t>
         </is>
       </c>
       <c r="P77" t="n">
-        <v>22.9</v>
+        <v>33.5</v>
       </c>
       <c r="Q77" t="n">
-        <v>48.1</v>
+        <v>53.4</v>
       </c>
       <c r="R77" t="n">
-        <v>42.1</v>
+        <v>47.1</v>
       </c>
       <c r="S77" t="n">
-        <v>94.90000000000001</v>
+        <v>52.4</v>
       </c>
       <c r="T77" t="n">
-        <v>75</v>
+        <v>50</v>
       </c>
       <c r="U77" t="n">
-        <v>28.9</v>
+        <v>79.90000000000001</v>
       </c>
       <c r="V77" t="inlineStr">
         <is>
@@ -21823,7 +21823,7 @@
       </c>
       <c r="X77" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>8</t>
         </is>
       </c>
       <c r="Y77" t="inlineStr">
@@ -21844,7 +21844,7 @@
       <c r="AB77" t="inlineStr"/>
       <c r="AC77" t="inlineStr">
         <is>
-          <t>H:2026 P:2026/2025</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD77" t="inlineStr"/>
@@ -21866,22 +21866,22 @@
       </c>
       <c r="AI77" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>14</t>
         </is>
       </c>
       <c r="AJ77" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AK77" t="inlineStr">
         <is>
-          <t>Last 7 games: 4/21, 1 HR</t>
+          <t>Hot streak: 3 HR in last 7 games</t>
         </is>
       </c>
       <c r="AL77" t="inlineStr">
         <is>
-          <t>switch hitter; pitcher baseline 8.9% barrel, 19.7 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 9.5% barrel, 20.4 HR allowed</t>
         </is>
       </c>
       <c r="AM77" t="inlineStr">
@@ -21891,32 +21891,32 @@
       </c>
       <c r="AN77" t="inlineStr">
         <is>
-          <t>4.1</t>
+          <t>8.18</t>
         </is>
       </c>
       <c r="AO77" t="inlineStr">
         <is>
-          <t>41.2</t>
+          <t>36.68</t>
         </is>
       </c>
       <c r="AP77" t="inlineStr">
         <is>
-          <t>89.1</t>
+          <t>88.87</t>
         </is>
       </c>
       <c r="AQ77" t="inlineStr">
         <is>
-          <t>100.1991</t>
+          <t>99.4568</t>
         </is>
       </c>
       <c r="AR77" t="inlineStr">
         <is>
-          <t>0.371</t>
+          <t>0.3877</t>
         </is>
       </c>
       <c r="AS77" t="inlineStr">
         <is>
-          <t>0.131</t>
+          <t>0.1635</t>
         </is>
       </c>
       <c r="AT77" t="inlineStr">
@@ -21926,77 +21926,77 @@
       </c>
       <c r="AU77" t="inlineStr">
         <is>
-          <t>69.8</t>
+          <t>72.34</t>
         </is>
       </c>
       <c r="AV77" t="inlineStr">
         <is>
-          <t>8.8</t>
+          <t>21.05</t>
         </is>
       </c>
       <c r="AW77" t="inlineStr">
         <is>
-          <t>36.5</t>
+          <t>41.58</t>
         </is>
       </c>
       <c r="AX77" t="inlineStr">
         <is>
-          <t>19.4</t>
+          <t>32.16</t>
         </is>
       </c>
       <c r="AY77" t="inlineStr">
         <is>
-          <t>5.0</t>
+          <t>5.4</t>
         </is>
       </c>
       <c r="AZ77" t="inlineStr">
         <is>
-          <t>0.141</t>
+          <t>0.1506</t>
         </is>
       </c>
       <c r="BA77" t="inlineStr">
         <is>
-          <t>8.95</t>
+          <t>9.48</t>
         </is>
       </c>
       <c r="BB77" t="inlineStr">
         <is>
-          <t>44.7</t>
+          <t>41.52</t>
         </is>
       </c>
       <c r="BC77" t="inlineStr">
         <is>
-          <t>90.52</t>
+          <t>90.39</t>
         </is>
       </c>
       <c r="BD77" t="inlineStr">
         <is>
-          <t>0.3945</t>
+          <t>0.4482</t>
         </is>
       </c>
       <c r="BE77" t="inlineStr">
         <is>
-          <t>0.1644</t>
+          <t>0.1815</t>
         </is>
       </c>
       <c r="BF77" t="inlineStr">
         <is>
-          <t>29.74</t>
+          <t>29.01</t>
         </is>
       </c>
       <c r="BG77" t="inlineStr">
         <is>
-          <t>In From CF</t>
+          <t>L To R</t>
         </is>
       </c>
       <c r="BH77" t="inlineStr">
         <is>
-          <t>77</t>
+          <t>85</t>
         </is>
       </c>
       <c r="BI77" t="inlineStr">
         <is>
-          <t>Rate Field</t>
+          <t>Busch Stadium</t>
         </is>
       </c>
       <c r="BJ77" t="inlineStr"/>
@@ -22007,52 +22007,52 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>687637</t>
+          <t>663993</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Dylan Beavers</t>
+          <t>Nathaniel Lowe</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>BAL</t>
+          <t>CLE</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>STL</t>
+          <t>LAA</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>2026-08-25T23:45:00Z</t>
+          <t>2026-08-26T01:38:00Z</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Warmup</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>5</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>Matthew Liberatore</t>
+          <t>Walbert Ureña</t>
         </is>
       </c>
       <c r="J78" t="inlineStr">
         <is>
-          <t>669461</t>
+          <t>700712</t>
         </is>
       </c>
       <c r="K78" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>R</t>
         </is>
       </c>
       <c r="L78" t="n">
@@ -22070,26 +22070,26 @@
       </c>
       <c r="O78" t="inlineStr">
         <is>
-          <t>Hot Hitter/Streak</t>
+          <t>Good Environment, Platoon Edge</t>
         </is>
       </c>
       <c r="P78" t="n">
-        <v>33.5</v>
+        <v>37</v>
       </c>
       <c r="Q78" t="n">
-        <v>53.4</v>
+        <v>16.7</v>
       </c>
       <c r="R78" t="n">
-        <v>47.1</v>
+        <v>71.2</v>
       </c>
       <c r="S78" t="n">
-        <v>52.4</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="T78" t="n">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="U78" t="n">
-        <v>79.90000000000001</v>
+        <v>10.8</v>
       </c>
       <c r="V78" t="inlineStr">
         <is>
@@ -22103,7 +22103,7 @@
       </c>
       <c r="X78" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>5</t>
         </is>
       </c>
       <c r="Y78" t="inlineStr">
@@ -22124,7 +22124,7 @@
       <c r="AB78" t="inlineStr"/>
       <c r="AC78" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026/2025</t>
+          <t>H:2026/2025 P:2026</t>
         </is>
       </c>
       <c r="AD78" t="inlineStr"/>
@@ -22141,27 +22141,27 @@
       </c>
       <c r="AH78" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AI78" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>26</t>
         </is>
       </c>
       <c r="AJ78" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK78" t="inlineStr">
         <is>
-          <t>Hot streak: 3 HR in last 7 games</t>
+          <t>Last 7 games: 5/26, 0 HR</t>
         </is>
       </c>
       <c r="AL78" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 9.5% barrel, 20.4 HR allowed</t>
+          <t>platoon edge; pitcher baseline 5.3% barrel, 7.0 HR allowed</t>
         </is>
       </c>
       <c r="AM78" t="inlineStr">
@@ -22171,112 +22171,112 @@
       </c>
       <c r="AN78" t="inlineStr">
         <is>
-          <t>8.18</t>
+          <t>8.33</t>
         </is>
       </c>
       <c r="AO78" t="inlineStr">
         <is>
-          <t>36.68</t>
+          <t>41.5</t>
         </is>
       </c>
       <c r="AP78" t="inlineStr">
         <is>
-          <t>88.87</t>
+          <t>89.14</t>
         </is>
       </c>
       <c r="AQ78" t="inlineStr">
         <is>
-          <t>99.4568</t>
+          <t>100.9008</t>
         </is>
       </c>
       <c r="AR78" t="inlineStr">
         <is>
-          <t>0.3877</t>
+          <t>0.4213</t>
         </is>
       </c>
       <c r="AS78" t="inlineStr">
         <is>
-          <t>0.1635</t>
+          <t>0.166</t>
         </is>
       </c>
       <c r="AT78" t="inlineStr">
         <is>
-          <t>0.316</t>
+          <t>0.3275</t>
         </is>
       </c>
       <c r="AU78" t="inlineStr">
         <is>
-          <t>72.34</t>
+          <t>74.0</t>
         </is>
       </c>
       <c r="AV78" t="inlineStr">
         <is>
-          <t>21.05</t>
+          <t>39.5</t>
         </is>
       </c>
       <c r="AW78" t="inlineStr">
         <is>
-          <t>41.58</t>
+          <t>35.17</t>
         </is>
       </c>
       <c r="AX78" t="inlineStr">
         <is>
-          <t>32.16</t>
+          <t>26.41</t>
         </is>
       </c>
       <c r="AY78" t="inlineStr">
         <is>
-          <t>5.4</t>
+          <t>15.2</t>
         </is>
       </c>
       <c r="AZ78" t="inlineStr">
         <is>
-          <t>0.1506</t>
+          <t>0.1908</t>
         </is>
       </c>
       <c r="BA78" t="inlineStr">
         <is>
-          <t>9.48</t>
+          <t>5.3</t>
         </is>
       </c>
       <c r="BB78" t="inlineStr">
         <is>
-          <t>41.52</t>
+          <t>34.3</t>
         </is>
       </c>
       <c r="BC78" t="inlineStr">
         <is>
-          <t>90.39</t>
+          <t>87.2</t>
         </is>
       </c>
       <c r="BD78" t="inlineStr">
         <is>
-          <t>0.4482</t>
+          <t>0.301</t>
         </is>
       </c>
       <c r="BE78" t="inlineStr">
         <is>
-          <t>0.1815</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="BF78" t="inlineStr">
         <is>
-          <t>29.01</t>
+          <t>23.1</t>
         </is>
       </c>
       <c r="BG78" t="inlineStr">
         <is>
-          <t>L To R</t>
+          <t>Out To CF</t>
         </is>
       </c>
       <c r="BH78" t="inlineStr">
         <is>
-          <t>85</t>
+          <t>90</t>
         </is>
       </c>
       <c r="BI78" t="inlineStr">
         <is>
-          <t>Busch Stadium</t>
+          <t>Angel Stadium</t>
         </is>
       </c>
       <c r="BJ78" t="inlineStr"/>
@@ -22287,47 +22287,47 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>663993</t>
+          <t>695731</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Nathaniel Lowe</t>
+          <t>Braden Montgomery</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>CLE</t>
+          <t>CWS</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>LAA</t>
+          <t>TEX</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>2026-08-26T01:38:00Z</t>
+          <t>2026-08-25T23:40:00Z</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>Walbert Ureña</t>
+          <t>Jacob deGrom</t>
         </is>
       </c>
       <c r="J79" t="inlineStr">
         <is>
-          <t>700712</t>
+          <t>594798</t>
         </is>
       </c>
       <c r="K79" t="inlineStr">
@@ -22336,7 +22336,7 @@
         </is>
       </c>
       <c r="L79" t="n">
-        <v>46.8</v>
+        <v>46.7</v>
       </c>
       <c r="M79" t="inlineStr">
         <is>
@@ -22350,26 +22350,26 @@
       </c>
       <c r="O79" t="inlineStr">
         <is>
-          <t>Good Environment, Platoon Edge</t>
+          <t>Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P79" t="n">
-        <v>37</v>
+        <v>22.9</v>
       </c>
       <c r="Q79" t="n">
-        <v>16.7</v>
+        <v>48.1</v>
       </c>
       <c r="R79" t="n">
-        <v>71.2</v>
+        <v>40.6</v>
       </c>
       <c r="S79" t="n">
-        <v>86.40000000000001</v>
+        <v>94.90000000000001</v>
       </c>
       <c r="T79" t="n">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="U79" t="n">
-        <v>10.8</v>
+        <v>28.9</v>
       </c>
       <c r="V79" t="inlineStr">
         <is>
@@ -22383,7 +22383,7 @@
       </c>
       <c r="X79" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="Y79" t="inlineStr">
@@ -22404,7 +22404,7 @@
       <c r="AB79" t="inlineStr"/>
       <c r="AC79" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026</t>
+          <t>H:2026 P:2026/2025</t>
         </is>
       </c>
       <c r="AD79" t="inlineStr"/>
@@ -22421,27 +22421,27 @@
       </c>
       <c r="AH79" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AI79" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>21</t>
         </is>
       </c>
       <c r="AJ79" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AK79" t="inlineStr">
         <is>
-          <t>Last 7 games: 5/26, 0 HR</t>
+          <t>Last 7 games: 4/21, 1 HR</t>
         </is>
       </c>
       <c r="AL79" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 5.3% barrel, 7.0 HR allowed</t>
+          <t>switch hitter; pitcher baseline 8.9% barrel, 19.7 HR allowed</t>
         </is>
       </c>
       <c r="AM79" t="inlineStr">
@@ -22451,112 +22451,112 @@
       </c>
       <c r="AN79" t="inlineStr">
         <is>
-          <t>8.33</t>
+          <t>4.1</t>
         </is>
       </c>
       <c r="AO79" t="inlineStr">
         <is>
-          <t>41.5</t>
+          <t>41.2</t>
         </is>
       </c>
       <c r="AP79" t="inlineStr">
         <is>
-          <t>89.14</t>
+          <t>89.1</t>
         </is>
       </c>
       <c r="AQ79" t="inlineStr">
         <is>
-          <t>100.9008</t>
+          <t>100.1991</t>
         </is>
       </c>
       <c r="AR79" t="inlineStr">
         <is>
-          <t>0.4213</t>
+          <t>0.371</t>
         </is>
       </c>
       <c r="AS79" t="inlineStr">
         <is>
-          <t>0.166</t>
+          <t>0.131</t>
         </is>
       </c>
       <c r="AT79" t="inlineStr">
         <is>
-          <t>0.3275</t>
+          <t>0.316</t>
         </is>
       </c>
       <c r="AU79" t="inlineStr">
         <is>
-          <t>74.0</t>
+          <t>69.8</t>
         </is>
       </c>
       <c r="AV79" t="inlineStr">
         <is>
-          <t>39.5</t>
+          <t>8.8</t>
         </is>
       </c>
       <c r="AW79" t="inlineStr">
         <is>
-          <t>35.17</t>
+          <t>36.5</t>
         </is>
       </c>
       <c r="AX79" t="inlineStr">
         <is>
-          <t>26.41</t>
+          <t>19.4</t>
         </is>
       </c>
       <c r="AY79" t="inlineStr">
         <is>
-          <t>15.2</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="AZ79" t="inlineStr">
         <is>
-          <t>0.1908</t>
+          <t>0.141</t>
         </is>
       </c>
       <c r="BA79" t="inlineStr">
         <is>
-          <t>5.3</t>
+          <t>8.95</t>
         </is>
       </c>
       <c r="BB79" t="inlineStr">
         <is>
-          <t>34.3</t>
+          <t>44.7</t>
         </is>
       </c>
       <c r="BC79" t="inlineStr">
         <is>
-          <t>87.2</t>
+          <t>90.52</t>
         </is>
       </c>
       <c r="BD79" t="inlineStr">
         <is>
-          <t>0.301</t>
+          <t>0.3945</t>
         </is>
       </c>
       <c r="BE79" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>0.1644</t>
         </is>
       </c>
       <c r="BF79" t="inlineStr">
         <is>
-          <t>23.1</t>
+          <t>29.74</t>
         </is>
       </c>
       <c r="BG79" t="inlineStr">
         <is>
-          <t>Out To CF</t>
+          <t>In From CF</t>
         </is>
       </c>
       <c r="BH79" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>78</t>
         </is>
       </c>
       <c r="BI79" t="inlineStr">
         <is>
-          <t>Angel Stadium</t>
+          <t>Rate Field</t>
         </is>
       </c>
       <c r="BJ79" t="inlineStr"/>
@@ -25363,47 +25363,47 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>803011</t>
+          <t>672515</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Sam Antonacci</t>
+          <t>Gabriel Moreno</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>CWS</t>
+          <t>AZ</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>TEX</t>
+          <t>CHC</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>2026-08-25T23:40:00Z</t>
+          <t>2026-08-26T01:40:00Z</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Warmup</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>Jacob deGrom</t>
+          <t>Clay Holmes</t>
         </is>
       </c>
       <c r="J90" t="inlineStr">
         <is>
-          <t>594798</t>
+          <t>605280</t>
         </is>
       </c>
       <c r="K90" t="inlineStr">
@@ -25426,50 +25426,42 @@
       </c>
       <c r="O90" t="inlineStr">
         <is>
-          <t>Premium Lineup Spot, Platoon Edge</t>
+          <t>Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P90" t="n">
-        <v>19.6</v>
+        <v>37</v>
       </c>
       <c r="Q90" t="n">
-        <v>50.2</v>
+        <v>29.2</v>
       </c>
       <c r="R90" t="n">
-        <v>42.1</v>
+        <v>41.7</v>
       </c>
       <c r="S90" t="n">
-        <v>93.2</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="T90" t="n">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="U90" t="n">
-        <v>2.5</v>
+        <v>34.9</v>
       </c>
       <c r="V90" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="W90" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="X90" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="W90" t="inlineStr"/>
+      <c r="X90" t="inlineStr"/>
       <c r="Y90" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="Z90" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="AA90" t="inlineStr">
@@ -25477,10 +25469,14 @@
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB90" t="inlineStr"/>
+      <c r="AB90" t="inlineStr">
+        <is>
+          <t>not found on RotoWire</t>
+        </is>
+      </c>
       <c r="AC90" t="inlineStr">
         <is>
-          <t>H:2026 P:2026/2025</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD90" t="inlineStr"/>
@@ -25497,27 +25493,27 @@
       </c>
       <c r="AH90" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AI90" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>26</t>
         </is>
       </c>
       <c r="AJ90" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AK90" t="inlineStr">
         <is>
-          <t>Last 7 games: 3/22, 0 HR</t>
+          <t>Last 7 games: 6/26, 1 HR</t>
         </is>
       </c>
       <c r="AL90" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 8.9% barrel, 19.7 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 5.5% barrel, 7.0 HR allowed</t>
         </is>
       </c>
       <c r="AM90" t="inlineStr">
@@ -25527,112 +25523,112 @@
       </c>
       <c r="AN90" t="inlineStr">
         <is>
-          <t>5.4</t>
+          <t>7.73</t>
         </is>
       </c>
       <c r="AO90" t="inlineStr">
         <is>
-          <t>33.5</t>
+          <t>42.91</t>
         </is>
       </c>
       <c r="AP90" t="inlineStr">
         <is>
-          <t>87.4</t>
+          <t>89.7</t>
         </is>
       </c>
       <c r="AQ90" t="inlineStr">
         <is>
-          <t>97.7459</t>
+          <t>99.7102</t>
         </is>
       </c>
       <c r="AR90" t="inlineStr">
         <is>
-          <t>0.392</t>
+          <t>0.4558</t>
         </is>
       </c>
       <c r="AS90" t="inlineStr">
         <is>
-          <t>0.12</t>
+          <t>0.1677</t>
         </is>
       </c>
       <c r="AT90" t="inlineStr">
         <is>
-          <t>0.341</t>
+          <t>0.3614</t>
         </is>
       </c>
       <c r="AU90" t="inlineStr">
         <is>
-          <t>69.9</t>
+          <t>71.39</t>
         </is>
       </c>
       <c r="AV90" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>19.93</t>
         </is>
       </c>
       <c r="AW90" t="inlineStr">
         <is>
-          <t>33.8</t>
+          <t>34.8</t>
         </is>
       </c>
       <c r="AX90" t="inlineStr">
         <is>
-          <t>21.7</t>
+          <t>25.89</t>
         </is>
       </c>
       <c r="AY90" t="inlineStr">
         <is>
-          <t>8.0</t>
+          <t>9.7</t>
         </is>
       </c>
       <c r="AZ90" t="inlineStr">
         <is>
-          <t>0.121</t>
+          <t>0.1557</t>
         </is>
       </c>
       <c r="BA90" t="inlineStr">
         <is>
-          <t>8.95</t>
+          <t>5.47</t>
         </is>
       </c>
       <c r="BB90" t="inlineStr">
         <is>
-          <t>44.7</t>
+          <t>42.02</t>
         </is>
       </c>
       <c r="BC90" t="inlineStr">
         <is>
-          <t>90.52</t>
+          <t>89.56</t>
         </is>
       </c>
       <c r="BD90" t="inlineStr">
         <is>
-          <t>0.3945</t>
+          <t>0.3786</t>
         </is>
       </c>
       <c r="BE90" t="inlineStr">
         <is>
-          <t>0.1644</t>
+          <t>0.1241</t>
         </is>
       </c>
       <c r="BF90" t="inlineStr">
         <is>
-          <t>29.74</t>
+          <t>18.9</t>
         </is>
       </c>
       <c r="BG90" t="inlineStr">
         <is>
-          <t>In From CF</t>
+          <t>None</t>
         </is>
       </c>
       <c r="BH90" t="inlineStr">
         <is>
-          <t>77</t>
+          <t>72</t>
         </is>
       </c>
       <c r="BI90" t="inlineStr">
         <is>
-          <t>Rate Field</t>
+          <t>Chase Field</t>
         </is>
       </c>
       <c r="BJ90" t="inlineStr"/>
@@ -25643,47 +25639,47 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>672515</t>
+          <t>803011</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Gabriel Moreno</t>
+          <t>Sam Antonacci</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>AZ</t>
+          <t>CWS</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>CHC</t>
+          <t>TEX</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>2026-08-26T01:40:00Z</t>
+          <t>2026-08-25T23:40:00Z</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t>Clay Holmes</t>
+          <t>Jacob deGrom</t>
         </is>
       </c>
       <c r="J91" t="inlineStr">
         <is>
-          <t>605280</t>
+          <t>594798</t>
         </is>
       </c>
       <c r="K91" t="inlineStr">
@@ -25692,7 +25688,7 @@
         </is>
       </c>
       <c r="L91" t="n">
-        <v>45.2</v>
+        <v>45</v>
       </c>
       <c r="M91" t="inlineStr">
         <is>
@@ -25706,57 +25702,61 @@
       </c>
       <c r="O91" t="inlineStr">
         <is>
-          <t>Premium Lineup Spot</t>
+          <t>Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P91" t="n">
-        <v>37</v>
+        <v>19.6</v>
       </c>
       <c r="Q91" t="n">
-        <v>29.2</v>
+        <v>50.2</v>
       </c>
       <c r="R91" t="n">
-        <v>41.7</v>
+        <v>40.6</v>
       </c>
       <c r="S91" t="n">
-        <v>96.59999999999999</v>
+        <v>93.2</v>
       </c>
       <c r="T91" t="n">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="U91" t="n">
-        <v>34.9</v>
+        <v>2.5</v>
       </c>
       <c r="V91" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="W91" t="inlineStr"/>
-      <c r="X91" t="inlineStr"/>
+      <c r="W91" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X91" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="Y91" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z91" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Z91" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA91" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB91" t="inlineStr">
-        <is>
-          <t>not found on RotoWire</t>
-        </is>
-      </c>
+      <c r="AB91" t="inlineStr"/>
       <c r="AC91" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026/2025</t>
+          <t>H:2026 P:2026/2025</t>
         </is>
       </c>
       <c r="AD91" t="inlineStr"/>
@@ -25773,27 +25773,27 @@
       </c>
       <c r="AH91" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AI91" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>22</t>
         </is>
       </c>
       <c r="AJ91" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK91" t="inlineStr">
         <is>
-          <t>Last 7 games: 6/26, 1 HR</t>
+          <t>Last 7 games: 3/22, 0 HR</t>
         </is>
       </c>
       <c r="AL91" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 5.5% barrel, 7.0 HR allowed</t>
+          <t>platoon edge; pitcher baseline 8.9% barrel, 19.7 HR allowed</t>
         </is>
       </c>
       <c r="AM91" t="inlineStr">
@@ -25803,112 +25803,112 @@
       </c>
       <c r="AN91" t="inlineStr">
         <is>
-          <t>7.73</t>
+          <t>5.4</t>
         </is>
       </c>
       <c r="AO91" t="inlineStr">
         <is>
-          <t>42.91</t>
+          <t>33.5</t>
         </is>
       </c>
       <c r="AP91" t="inlineStr">
         <is>
-          <t>89.7</t>
+          <t>87.4</t>
         </is>
       </c>
       <c r="AQ91" t="inlineStr">
         <is>
-          <t>99.7102</t>
+          <t>97.7459</t>
         </is>
       </c>
       <c r="AR91" t="inlineStr">
         <is>
-          <t>0.4558</t>
+          <t>0.392</t>
         </is>
       </c>
       <c r="AS91" t="inlineStr">
         <is>
-          <t>0.1677</t>
+          <t>0.12</t>
         </is>
       </c>
       <c r="AT91" t="inlineStr">
         <is>
-          <t>0.3614</t>
+          <t>0.341</t>
         </is>
       </c>
       <c r="AU91" t="inlineStr">
         <is>
-          <t>71.39</t>
+          <t>69.9</t>
         </is>
       </c>
       <c r="AV91" t="inlineStr">
         <is>
-          <t>19.93</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="AW91" t="inlineStr">
         <is>
-          <t>34.8</t>
+          <t>33.8</t>
         </is>
       </c>
       <c r="AX91" t="inlineStr">
         <is>
-          <t>25.89</t>
+          <t>21.7</t>
         </is>
       </c>
       <c r="AY91" t="inlineStr">
         <is>
-          <t>9.7</t>
+          <t>8.0</t>
         </is>
       </c>
       <c r="AZ91" t="inlineStr">
         <is>
-          <t>0.1557</t>
+          <t>0.121</t>
         </is>
       </c>
       <c r="BA91" t="inlineStr">
         <is>
-          <t>5.47</t>
+          <t>8.95</t>
         </is>
       </c>
       <c r="BB91" t="inlineStr">
         <is>
-          <t>42.02</t>
+          <t>44.7</t>
         </is>
       </c>
       <c r="BC91" t="inlineStr">
         <is>
-          <t>89.56</t>
+          <t>90.52</t>
         </is>
       </c>
       <c r="BD91" t="inlineStr">
         <is>
-          <t>0.3786</t>
+          <t>0.3945</t>
         </is>
       </c>
       <c r="BE91" t="inlineStr">
         <is>
-          <t>0.1241</t>
+          <t>0.1644</t>
         </is>
       </c>
       <c r="BF91" t="inlineStr">
         <is>
-          <t>18.9</t>
+          <t>29.74</t>
         </is>
       </c>
       <c r="BG91" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>In From CF</t>
         </is>
       </c>
       <c r="BH91" t="inlineStr">
         <is>
-          <t>72</t>
+          <t>78</t>
         </is>
       </c>
       <c r="BI91" t="inlineStr">
         <is>
-          <t>Chase Field</t>
+          <t>Rate Field</t>
         </is>
       </c>
       <c r="BJ91" t="inlineStr"/>
@@ -26528,7 +26528,7 @@
         </is>
       </c>
       <c r="L94" t="n">
-        <v>44.5</v>
+        <v>44.3</v>
       </c>
       <c r="M94" t="inlineStr">
         <is>
@@ -26552,7 +26552,7 @@
         <v>38.5</v>
       </c>
       <c r="R94" t="n">
-        <v>42.1</v>
+        <v>40.6</v>
       </c>
       <c r="S94" t="n">
         <v>86.40000000000001</v>
@@ -26743,7 +26743,7 @@
       </c>
       <c r="BH94" t="inlineStr">
         <is>
-          <t>77</t>
+          <t>78</t>
         </is>
       </c>
       <c r="BI94" t="inlineStr">
@@ -26759,56 +26759,56 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>681351</t>
+          <t>683953</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Logan O'Hoppe</t>
+          <t>Travis Bazzana</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>TEX</t>
+          <t>CLE</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>CWS</t>
+          <t>LAA</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>2026-08-25T23:40:00Z</t>
+          <t>2026-08-26T01:38:00Z</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Warmup</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t>Anthony Kay</t>
+          <t>Walbert Ureña</t>
         </is>
       </c>
       <c r="J95" t="inlineStr">
         <is>
-          <t>641743</t>
+          <t>700712</t>
         </is>
       </c>
       <c r="K95" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>R</t>
         </is>
       </c>
       <c r="L95" t="n">
-        <v>44</v>
+        <v>43.9</v>
       </c>
       <c r="M95" t="inlineStr">
         <is>
@@ -26822,26 +26822,26 @@
       </c>
       <c r="O95" t="inlineStr">
         <is>
-          <t>Strong Barrel, Platoon Edge</t>
+          <t>Good Environment, Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P95" t="n">
-        <v>34.9</v>
+        <v>20.9</v>
       </c>
       <c r="Q95" t="n">
-        <v>38.5</v>
+        <v>16.7</v>
       </c>
       <c r="R95" t="n">
-        <v>42.1</v>
+        <v>71.2</v>
       </c>
       <c r="S95" t="n">
-        <v>64.3</v>
+        <v>100</v>
       </c>
       <c r="T95" t="n">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="U95" t="n">
-        <v>17.7</v>
+        <v>22.4</v>
       </c>
       <c r="V95" t="inlineStr">
         <is>
@@ -26855,7 +26855,7 @@
       </c>
       <c r="X95" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>2</t>
         </is>
       </c>
       <c r="Y95" t="inlineStr">
@@ -26876,7 +26876,7 @@
       <c r="AB95" t="inlineStr"/>
       <c r="AC95" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026</t>
+          <t>H:2026 P:2026</t>
         </is>
       </c>
       <c r="AD95" t="inlineStr"/>
@@ -26893,12 +26893,12 @@
       </c>
       <c r="AH95" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AI95" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>26</t>
         </is>
       </c>
       <c r="AJ95" t="inlineStr">
@@ -26908,12 +26908,12 @@
       </c>
       <c r="AK95" t="inlineStr">
         <is>
-          <t>Last 7 games: 5/21, 0 HR</t>
+          <t>Last 7 games: 7/26, 0 HR</t>
         </is>
       </c>
       <c r="AL95" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 8.2% barrel, 16.0 HR allowed</t>
+          <t>platoon edge; pitcher baseline 5.3% barrel, 7.0 HR allowed</t>
         </is>
       </c>
       <c r="AM95" t="inlineStr">
@@ -26923,112 +26923,112 @@
       </c>
       <c r="AN95" t="inlineStr">
         <is>
-          <t>10.78</t>
+          <t>4.7</t>
         </is>
       </c>
       <c r="AO95" t="inlineStr">
         <is>
-          <t>38.85</t>
+          <t>36.8</t>
         </is>
       </c>
       <c r="AP95" t="inlineStr">
         <is>
-          <t>88.17</t>
+          <t>88.1</t>
         </is>
       </c>
       <c r="AQ95" t="inlineStr">
         <is>
-          <t>99.6818</t>
+          <t>98.5252</t>
         </is>
       </c>
       <c r="AR95" t="inlineStr">
         <is>
-          <t>0.3585</t>
+          <t>0.351</t>
         </is>
       </c>
       <c r="AS95" t="inlineStr">
         <is>
-          <t>0.1508</t>
+          <t>0.123</t>
         </is>
       </c>
       <c r="AT95" t="inlineStr">
         <is>
-          <t>0.2758</t>
+          <t>0.302</t>
         </is>
       </c>
       <c r="AU95" t="inlineStr">
         <is>
-          <t>72.04</t>
+          <t>69.7</t>
         </is>
       </c>
       <c r="AV95" t="inlineStr">
         <is>
-          <t>23.98</t>
+          <t>12.5</t>
         </is>
       </c>
       <c r="AW95" t="inlineStr">
         <is>
-          <t>44.24</t>
+          <t>38.3</t>
         </is>
       </c>
       <c r="AX95" t="inlineStr">
         <is>
-          <t>29.7</t>
+          <t>27.4</t>
         </is>
       </c>
       <c r="AY95" t="inlineStr">
         <is>
-          <t>8.5</t>
+          <t>9.0</t>
         </is>
       </c>
       <c r="AZ95" t="inlineStr">
         <is>
-          <t>0.1062</t>
+          <t>0.13</t>
         </is>
       </c>
       <c r="BA95" t="inlineStr">
         <is>
-          <t>8.2</t>
+          <t>5.3</t>
         </is>
       </c>
       <c r="BB95" t="inlineStr">
         <is>
-          <t>39.7</t>
+          <t>34.3</t>
         </is>
       </c>
       <c r="BC95" t="inlineStr">
         <is>
-          <t>88.4</t>
+          <t>87.2</t>
         </is>
       </c>
       <c r="BD95" t="inlineStr">
         <is>
-          <t>0.404</t>
+          <t>0.301</t>
         </is>
       </c>
       <c r="BE95" t="inlineStr">
         <is>
-          <t>0.144</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="BF95" t="inlineStr">
         <is>
-          <t>21.8</t>
+          <t>23.1</t>
         </is>
       </c>
       <c r="BG95" t="inlineStr">
         <is>
-          <t>In From CF</t>
+          <t>Out To CF</t>
         </is>
       </c>
       <c r="BH95" t="inlineStr">
         <is>
-          <t>77</t>
+          <t>90</t>
         </is>
       </c>
       <c r="BI95" t="inlineStr">
         <is>
-          <t>Rate Field</t>
+          <t>Angel Stadium</t>
         </is>
       </c>
       <c r="BJ95" t="inlineStr"/>
@@ -27039,27 +27039,27 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>683953</t>
+          <t>686797</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Travis Bazzana</t>
+          <t>Brooks Lee</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>CLE</t>
+          <t>MIN</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>LAA</t>
+          <t>ATH</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>2026-08-26T01:38:00Z</t>
+          <t>2026-08-26T01:40:00Z</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
@@ -27069,22 +27069,22 @@
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>7</t>
         </is>
       </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t>Walbert Ureña</t>
+          <t>Gage Jump</t>
         </is>
       </c>
       <c r="J96" t="inlineStr">
         <is>
-          <t>700712</t>
+          <t>695611</t>
         </is>
       </c>
       <c r="K96" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>L</t>
         </is>
       </c>
       <c r="L96" t="n">
@@ -27102,26 +27102,26 @@
       </c>
       <c r="O96" t="inlineStr">
         <is>
-          <t>Good Environment, Premium Lineup Spot, Platoon Edge</t>
+          <t>Good Environment, Platoon Edge</t>
         </is>
       </c>
       <c r="P96" t="n">
-        <v>20.9</v>
+        <v>19.7</v>
       </c>
       <c r="Q96" t="n">
-        <v>16.7</v>
+        <v>31.1</v>
       </c>
       <c r="R96" t="n">
-        <v>71.2</v>
+        <v>74.40000000000001</v>
       </c>
       <c r="S96" t="n">
-        <v>100</v>
+        <v>64.3</v>
       </c>
       <c r="T96" t="n">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="U96" t="n">
-        <v>22.4</v>
+        <v>60.7</v>
       </c>
       <c r="V96" t="inlineStr">
         <is>
@@ -27135,7 +27135,7 @@
       </c>
       <c r="X96" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>7</t>
         </is>
       </c>
       <c r="Y96" t="inlineStr">
@@ -27156,7 +27156,7 @@
       <c r="AB96" t="inlineStr"/>
       <c r="AC96" t="inlineStr">
         <is>
-          <t>H:2026 P:2026</t>
+          <t>H:2026/2025 P:2026</t>
         </is>
       </c>
       <c r="AD96" t="inlineStr"/>
@@ -27178,22 +27178,22 @@
       </c>
       <c r="AI96" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>25</t>
         </is>
       </c>
       <c r="AJ96" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AK96" t="inlineStr">
         <is>
-          <t>Last 7 games: 7/26, 0 HR</t>
+          <t>Hot streak: 2 HR in last 7 games</t>
         </is>
       </c>
       <c r="AL96" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 5.3% barrel, 7.0 HR allowed</t>
+          <t>switch hitter; pitcher baseline 6.1% barrel, 9.0 HR allowed</t>
         </is>
       </c>
       <c r="AM96" t="inlineStr">
@@ -27203,97 +27203,97 @@
       </c>
       <c r="AN96" t="inlineStr">
         <is>
-          <t>4.7</t>
+          <t>4.47</t>
         </is>
       </c>
       <c r="AO96" t="inlineStr">
         <is>
-          <t>36.8</t>
+          <t>34.58</t>
         </is>
       </c>
       <c r="AP96" t="inlineStr">
         <is>
-          <t>88.1</t>
+          <t>88.11</t>
         </is>
       </c>
       <c r="AQ96" t="inlineStr">
         <is>
-          <t>98.5252</t>
+          <t>97.5322</t>
         </is>
       </c>
       <c r="AR96" t="inlineStr">
         <is>
-          <t>0.351</t>
+          <t>0.3467</t>
         </is>
       </c>
       <c r="AS96" t="inlineStr">
         <is>
-          <t>0.123</t>
+          <t>0.119</t>
         </is>
       </c>
       <c r="AT96" t="inlineStr">
         <is>
-          <t>0.302</t>
+          <t>0.2771</t>
         </is>
       </c>
       <c r="AU96" t="inlineStr">
         <is>
-          <t>69.7</t>
+          <t>69.92</t>
         </is>
       </c>
       <c r="AV96" t="inlineStr">
         <is>
-          <t>12.5</t>
+          <t>8.7</t>
         </is>
       </c>
       <c r="AW96" t="inlineStr">
         <is>
-          <t>38.3</t>
+          <t>42.34</t>
         </is>
       </c>
       <c r="AX96" t="inlineStr">
         <is>
-          <t>27.4</t>
+          <t>29.0</t>
         </is>
       </c>
       <c r="AY96" t="inlineStr">
         <is>
-          <t>9.0</t>
+          <t>18.8</t>
         </is>
       </c>
       <c r="AZ96" t="inlineStr">
         <is>
-          <t>0.13</t>
+          <t>0.169</t>
         </is>
       </c>
       <c r="BA96" t="inlineStr">
         <is>
-          <t>5.3</t>
+          <t>6.1</t>
         </is>
       </c>
       <c r="BB96" t="inlineStr">
         <is>
-          <t>34.3</t>
+          <t>38.7</t>
         </is>
       </c>
       <c r="BC96" t="inlineStr">
         <is>
-          <t>87.2</t>
+          <t>89.2</t>
         </is>
       </c>
       <c r="BD96" t="inlineStr">
         <is>
-          <t>0.301</t>
+          <t>0.392</t>
         </is>
       </c>
       <c r="BE96" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>0.133</t>
         </is>
       </c>
       <c r="BF96" t="inlineStr">
         <is>
-          <t>23.1</t>
+          <t>26.1</t>
         </is>
       </c>
       <c r="BG96" t="inlineStr">
@@ -27303,12 +27303,12 @@
       </c>
       <c r="BH96" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>93</t>
         </is>
       </c>
       <c r="BI96" t="inlineStr">
         <is>
-          <t>Angel Stadium</t>
+          <t>Sutter Health Park</t>
         </is>
       </c>
       <c r="BJ96" t="inlineStr"/>
@@ -27319,22 +27319,22 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>686797</t>
+          <t>641487</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Brooks Lee</t>
+          <t>J.P. Crawford</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>MIN</t>
+          <t>SEA</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>ATH</t>
+          <t>PHI</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
@@ -27349,22 +27349,22 @@
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t>Gage Jump</t>
+          <t>Aaron Nola</t>
         </is>
       </c>
       <c r="J97" t="inlineStr">
         <is>
-          <t>695611</t>
+          <t>605400</t>
         </is>
       </c>
       <c r="K97" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>R</t>
         </is>
       </c>
       <c r="L97" t="n">
@@ -27382,26 +27382,26 @@
       </c>
       <c r="O97" t="inlineStr">
         <is>
-          <t>Good Environment, Platoon Edge</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P97" t="n">
-        <v>19.7</v>
+        <v>21.4</v>
       </c>
       <c r="Q97" t="n">
-        <v>31.1</v>
+        <v>49.1</v>
       </c>
       <c r="R97" t="n">
-        <v>74.40000000000001</v>
+        <v>68.40000000000001</v>
       </c>
       <c r="S97" t="n">
-        <v>64.3</v>
+        <v>52.4</v>
       </c>
       <c r="T97" t="n">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="U97" t="n">
-        <v>60.7</v>
+        <v>4.5</v>
       </c>
       <c r="V97" t="inlineStr">
         <is>
@@ -27415,7 +27415,7 @@
       </c>
       <c r="X97" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="Y97" t="inlineStr">
@@ -27436,7 +27436,7 @@
       <c r="AB97" t="inlineStr"/>
       <c r="AC97" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD97" t="inlineStr"/>
@@ -27453,27 +27453,27 @@
       </c>
       <c r="AH97" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AI97" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>20</t>
         </is>
       </c>
       <c r="AJ97" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK97" t="inlineStr">
         <is>
-          <t>Hot streak: 2 HR in last 7 games</t>
+          <t>Last 7 games: 3/20, 0 HR</t>
         </is>
       </c>
       <c r="AL97" t="inlineStr">
         <is>
-          <t>switch hitter; pitcher baseline 6.1% barrel, 9.0 HR allowed</t>
+          <t>platoon edge; pitcher baseline 9.4% barrel, 27.1 HR allowed</t>
         </is>
       </c>
       <c r="AM97" t="inlineStr">
@@ -27483,97 +27483,97 @@
       </c>
       <c r="AN97" t="inlineStr">
         <is>
-          <t>4.47</t>
+          <t>5.95</t>
         </is>
       </c>
       <c r="AO97" t="inlineStr">
         <is>
-          <t>34.58</t>
+          <t>35.12</t>
         </is>
       </c>
       <c r="AP97" t="inlineStr">
         <is>
-          <t>88.11</t>
+          <t>87.48</t>
         </is>
       </c>
       <c r="AQ97" t="inlineStr">
         <is>
-          <t>97.5322</t>
+          <t>98.2679</t>
         </is>
       </c>
       <c r="AR97" t="inlineStr">
         <is>
-          <t>0.3467</t>
+          <t>0.3713</t>
         </is>
       </c>
       <c r="AS97" t="inlineStr">
         <is>
-          <t>0.119</t>
+          <t>0.1235</t>
         </is>
       </c>
       <c r="AT97" t="inlineStr">
         <is>
-          <t>0.2771</t>
+          <t>0.3262</t>
         </is>
       </c>
       <c r="AU97" t="inlineStr">
         <is>
-          <t>69.92</t>
+          <t>71.28</t>
         </is>
       </c>
       <c r="AV97" t="inlineStr">
         <is>
-          <t>8.7</t>
+          <t>18.88</t>
         </is>
       </c>
       <c r="AW97" t="inlineStr">
         <is>
-          <t>42.34</t>
+          <t>35.7</t>
         </is>
       </c>
       <c r="AX97" t="inlineStr">
         <is>
-          <t>29.0</t>
+          <t>20.65</t>
         </is>
       </c>
       <c r="AY97" t="inlineStr">
         <is>
-          <t>18.8</t>
+          <t>10.6</t>
         </is>
       </c>
       <c r="AZ97" t="inlineStr">
         <is>
-          <t>0.169</t>
+          <t>0.1246</t>
         </is>
       </c>
       <c r="BA97" t="inlineStr">
         <is>
-          <t>6.1</t>
+          <t>9.38</t>
         </is>
       </c>
       <c r="BB97" t="inlineStr">
         <is>
-          <t>38.7</t>
+          <t>42.39</t>
         </is>
       </c>
       <c r="BC97" t="inlineStr">
         <is>
-          <t>89.2</t>
+          <t>88.98</t>
         </is>
       </c>
       <c r="BD97" t="inlineStr">
         <is>
-          <t>0.392</t>
+          <t>0.4191</t>
         </is>
       </c>
       <c r="BE97" t="inlineStr">
         <is>
-          <t>0.133</t>
+          <t>0.1738</t>
         </is>
       </c>
       <c r="BF97" t="inlineStr">
         <is>
-          <t>26.1</t>
+          <t>27.46</t>
         </is>
       </c>
       <c r="BG97" t="inlineStr">
@@ -27583,12 +27583,12 @@
       </c>
       <c r="BH97" t="inlineStr">
         <is>
-          <t>93</t>
+          <t>84</t>
         </is>
       </c>
       <c r="BI97" t="inlineStr">
         <is>
-          <t>Sutter Health Park</t>
+          <t>T-Mobile Park</t>
         </is>
       </c>
       <c r="BJ97" t="inlineStr"/>
@@ -27599,27 +27599,27 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>641487</t>
+          <t>687529</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>J.P. Crawford</t>
+          <t>Grant McCray</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>SEA</t>
+          <t>SF</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>PHI</t>
+          <t>CIN</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>2026-08-26T01:40:00Z</t>
+          <t>2026-08-26T01:45:00Z</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
@@ -27634,12 +27634,12 @@
       </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t>Aaron Nola</t>
+          <t>Brady Singer</t>
         </is>
       </c>
       <c r="J98" t="inlineStr">
         <is>
-          <t>605400</t>
+          <t>663903</t>
         </is>
       </c>
       <c r="K98" t="inlineStr">
@@ -27662,17 +27662,17 @@
       </c>
       <c r="O98" t="inlineStr">
         <is>
-          <t>Platoon Edge</t>
+          <t>Strong Barrel, Platoon Edge</t>
         </is>
       </c>
       <c r="P98" t="n">
-        <v>21.4</v>
+        <v>26</v>
       </c>
       <c r="Q98" t="n">
-        <v>49.1</v>
+        <v>51.7</v>
       </c>
       <c r="R98" t="n">
-        <v>68.40000000000001</v>
+        <v>55.8</v>
       </c>
       <c r="S98" t="n">
         <v>52.4</v>
@@ -27681,7 +27681,7 @@
         <v>80</v>
       </c>
       <c r="U98" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="V98" t="inlineStr">
         <is>
@@ -27733,12 +27733,12 @@
       </c>
       <c r="AH98" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AI98" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>15</t>
         </is>
       </c>
       <c r="AJ98" t="inlineStr">
@@ -27748,12 +27748,12 @@
       </c>
       <c r="AK98" t="inlineStr">
         <is>
-          <t>Last 7 games: 3/20, 0 HR</t>
+          <t>Last 7 games: 1/15, 0 HR</t>
         </is>
       </c>
       <c r="AL98" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 9.4% barrel, 27.1 HR allowed</t>
+          <t>platoon edge; pitcher baseline 9.5% barrel, 23.2 HR allowed</t>
         </is>
       </c>
       <c r="AM98" t="inlineStr">
@@ -27763,97 +27763,97 @@
       </c>
       <c r="AN98" t="inlineStr">
         <is>
-          <t>5.95</t>
+          <t>11.83</t>
         </is>
       </c>
       <c r="AO98" t="inlineStr">
         <is>
-          <t>35.12</t>
+          <t>26.25</t>
         </is>
       </c>
       <c r="AP98" t="inlineStr">
         <is>
-          <t>87.48</t>
+          <t>87.31</t>
         </is>
       </c>
       <c r="AQ98" t="inlineStr">
         <is>
-          <t>98.2679</t>
+          <t>98.3932</t>
         </is>
       </c>
       <c r="AR98" t="inlineStr">
         <is>
-          <t>0.3713</t>
+          <t>0.3126</t>
         </is>
       </c>
       <c r="AS98" t="inlineStr">
         <is>
-          <t>0.1235</t>
+          <t>0.1344</t>
         </is>
       </c>
       <c r="AT98" t="inlineStr">
         <is>
-          <t>0.3262</t>
+          <t>0.2683</t>
         </is>
       </c>
       <c r="AU98" t="inlineStr">
         <is>
-          <t>71.28</t>
+          <t>72.43</t>
         </is>
       </c>
       <c r="AV98" t="inlineStr">
         <is>
-          <t>18.88</t>
+          <t>26.11</t>
         </is>
       </c>
       <c r="AW98" t="inlineStr">
         <is>
-          <t>35.7</t>
+          <t>40.29</t>
         </is>
       </c>
       <c r="AX98" t="inlineStr">
         <is>
-          <t>20.65</t>
+          <t>21.28</t>
         </is>
       </c>
       <c r="AY98" t="inlineStr">
         <is>
-          <t>10.6</t>
+          <t>0.7</t>
         </is>
       </c>
       <c r="AZ98" t="inlineStr">
         <is>
-          <t>0.1246</t>
+          <t>0.1148</t>
         </is>
       </c>
       <c r="BA98" t="inlineStr">
         <is>
-          <t>9.38</t>
+          <t>9.47</t>
         </is>
       </c>
       <c r="BB98" t="inlineStr">
         <is>
-          <t>42.39</t>
+          <t>40.77</t>
         </is>
       </c>
       <c r="BC98" t="inlineStr">
         <is>
-          <t>88.98</t>
+          <t>90.58</t>
         </is>
       </c>
       <c r="BD98" t="inlineStr">
         <is>
-          <t>0.4191</t>
+          <t>0.4356</t>
         </is>
       </c>
       <c r="BE98" t="inlineStr">
         <is>
-          <t>0.1738</t>
+          <t>0.173</t>
         </is>
       </c>
       <c r="BF98" t="inlineStr">
         <is>
-          <t>27.46</t>
+          <t>27.63</t>
         </is>
       </c>
       <c r="BG98" t="inlineStr">
@@ -27863,12 +27863,12 @@
       </c>
       <c r="BH98" t="inlineStr">
         <is>
-          <t>84</t>
+          <t>65</t>
         </is>
       </c>
       <c r="BI98" t="inlineStr">
         <is>
-          <t>T-Mobile Park</t>
+          <t>Oracle Park</t>
         </is>
       </c>
       <c r="BJ98" t="inlineStr"/>
@@ -27879,56 +27879,56 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>687529</t>
+          <t>681351</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Grant McCray</t>
+          <t>Logan O'Hoppe</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>SF</t>
+          <t>TEX</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>CIN</t>
+          <t>CWS</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>2026-08-26T01:45:00Z</t>
+          <t>2026-08-25T23:40:00Z</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t>Brady Singer</t>
+          <t>Anthony Kay</t>
         </is>
       </c>
       <c r="J99" t="inlineStr">
         <is>
-          <t>663903</t>
+          <t>641743</t>
         </is>
       </c>
       <c r="K99" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>L</t>
         </is>
       </c>
       <c r="L99" t="n">
-        <v>43.9</v>
+        <v>43.8</v>
       </c>
       <c r="M99" t="inlineStr">
         <is>
@@ -27946,22 +27946,22 @@
         </is>
       </c>
       <c r="P99" t="n">
-        <v>26</v>
+        <v>34.9</v>
       </c>
       <c r="Q99" t="n">
-        <v>51.7</v>
+        <v>38.5</v>
       </c>
       <c r="R99" t="n">
-        <v>55.8</v>
+        <v>40.6</v>
       </c>
       <c r="S99" t="n">
-        <v>52.4</v>
+        <v>64.3</v>
       </c>
       <c r="T99" t="n">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="U99" t="n">
-        <v>0</v>
+        <v>17.7</v>
       </c>
       <c r="V99" t="inlineStr">
         <is>
@@ -27975,7 +27975,7 @@
       </c>
       <c r="X99" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="Y99" t="inlineStr">
@@ -27996,7 +27996,7 @@
       <c r="AB99" t="inlineStr"/>
       <c r="AC99" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026/2025</t>
+          <t>H:2026/2025 P:2026</t>
         </is>
       </c>
       <c r="AD99" t="inlineStr"/>
@@ -28013,12 +28013,12 @@
       </c>
       <c r="AH99" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AI99" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>21</t>
         </is>
       </c>
       <c r="AJ99" t="inlineStr">
@@ -28028,12 +28028,12 @@
       </c>
       <c r="AK99" t="inlineStr">
         <is>
-          <t>Last 7 games: 1/15, 0 HR</t>
+          <t>Last 7 games: 5/21, 0 HR</t>
         </is>
       </c>
       <c r="AL99" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 9.5% barrel, 23.2 HR allowed</t>
+          <t>platoon edge; pitcher baseline 8.2% barrel, 16.0 HR allowed</t>
         </is>
       </c>
       <c r="AM99" t="inlineStr">
@@ -28043,112 +28043,112 @@
       </c>
       <c r="AN99" t="inlineStr">
         <is>
-          <t>11.83</t>
+          <t>10.78</t>
         </is>
       </c>
       <c r="AO99" t="inlineStr">
         <is>
-          <t>26.25</t>
+          <t>38.85</t>
         </is>
       </c>
       <c r="AP99" t="inlineStr">
         <is>
-          <t>87.31</t>
+          <t>88.17</t>
         </is>
       </c>
       <c r="AQ99" t="inlineStr">
         <is>
-          <t>98.3932</t>
+          <t>99.6818</t>
         </is>
       </c>
       <c r="AR99" t="inlineStr">
         <is>
-          <t>0.3126</t>
+          <t>0.3585</t>
         </is>
       </c>
       <c r="AS99" t="inlineStr">
         <is>
-          <t>0.1344</t>
+          <t>0.1508</t>
         </is>
       </c>
       <c r="AT99" t="inlineStr">
         <is>
-          <t>0.2683</t>
+          <t>0.2758</t>
         </is>
       </c>
       <c r="AU99" t="inlineStr">
         <is>
-          <t>72.43</t>
+          <t>72.04</t>
         </is>
       </c>
       <c r="AV99" t="inlineStr">
         <is>
-          <t>26.11</t>
+          <t>23.98</t>
         </is>
       </c>
       <c r="AW99" t="inlineStr">
         <is>
-          <t>40.29</t>
+          <t>44.24</t>
         </is>
       </c>
       <c r="AX99" t="inlineStr">
         <is>
-          <t>21.28</t>
+          <t>29.7</t>
         </is>
       </c>
       <c r="AY99" t="inlineStr">
         <is>
-          <t>0.7</t>
+          <t>8.5</t>
         </is>
       </c>
       <c r="AZ99" t="inlineStr">
         <is>
-          <t>0.1148</t>
+          <t>0.1062</t>
         </is>
       </c>
       <c r="BA99" t="inlineStr">
         <is>
-          <t>9.47</t>
+          <t>8.2</t>
         </is>
       </c>
       <c r="BB99" t="inlineStr">
         <is>
-          <t>40.77</t>
+          <t>39.7</t>
         </is>
       </c>
       <c r="BC99" t="inlineStr">
         <is>
-          <t>90.58</t>
+          <t>88.4</t>
         </is>
       </c>
       <c r="BD99" t="inlineStr">
         <is>
-          <t>0.4356</t>
+          <t>0.404</t>
         </is>
       </c>
       <c r="BE99" t="inlineStr">
         <is>
-          <t>0.173</t>
+          <t>0.144</t>
         </is>
       </c>
       <c r="BF99" t="inlineStr">
         <is>
-          <t>27.63</t>
+          <t>21.8</t>
         </is>
       </c>
       <c r="BG99" t="inlineStr">
         <is>
-          <t>Out To CF</t>
+          <t>In From CF</t>
         </is>
       </c>
       <c r="BH99" t="inlineStr">
         <is>
-          <t>65</t>
+          <t>78</t>
         </is>
       </c>
       <c r="BI99" t="inlineStr">
         <is>
-          <t>Oracle Park</t>
+          <t>Rate Field</t>
         </is>
       </c>
       <c r="BJ99" t="inlineStr"/>
@@ -29275,47 +29275,47 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>671976</t>
+          <t>701852</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Tristan Peters</t>
+          <t>Drew Cavanaugh</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>CWS</t>
+          <t>SF</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>TEX</t>
+          <t>CIN</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>2026-08-25T23:40:00Z</t>
+          <t>2026-08-26T01:45:00Z</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Warmup</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>5</t>
         </is>
       </c>
       <c r="I104" t="inlineStr">
         <is>
-          <t>Jacob deGrom</t>
+          <t>Brady Singer</t>
         </is>
       </c>
       <c r="J104" t="inlineStr">
         <is>
-          <t>594798</t>
+          <t>663903</t>
         </is>
       </c>
       <c r="K104" t="inlineStr">
@@ -29338,26 +29338,26 @@
       </c>
       <c r="O104" t="inlineStr">
         <is>
-          <t>Platoon Edge, Hot Hitter/Streak</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P104" t="n">
-        <v>13.4</v>
+        <v>7</v>
       </c>
       <c r="Q104" t="n">
-        <v>50.2</v>
+        <v>51.7</v>
       </c>
       <c r="R104" t="n">
-        <v>42.1</v>
+        <v>55.8</v>
       </c>
       <c r="S104" t="n">
-        <v>64.3</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="T104" t="n">
         <v>80</v>
       </c>
       <c r="U104" t="n">
-        <v>76.09999999999999</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="V104" t="inlineStr">
         <is>
@@ -29371,7 +29371,7 @@
       </c>
       <c r="X104" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>5</t>
         </is>
       </c>
       <c r="Y104" t="inlineStr">
@@ -29392,7 +29392,7 @@
       <c r="AB104" t="inlineStr"/>
       <c r="AC104" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026/2025</t>
+          <t>H:2026 P:2026/2025</t>
         </is>
       </c>
       <c r="AD104" t="inlineStr"/>
@@ -29409,27 +29409,27 @@
       </c>
       <c r="AH104" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AI104" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>22</t>
         </is>
       </c>
       <c r="AJ104" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK104" t="inlineStr">
         <is>
-          <t>Hot streak: 3 HR in last 7 games</t>
+          <t>Last 7 games: 4/22, 0 HR</t>
         </is>
       </c>
       <c r="AL104" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 8.9% barrel, 19.7 HR allowed</t>
+          <t>platoon edge; pitcher baseline 9.5% barrel, 23.2 HR allowed</t>
         </is>
       </c>
       <c r="AM104" t="inlineStr">
@@ -29439,112 +29439,112 @@
       </c>
       <c r="AN104" t="inlineStr">
         <is>
-          <t>3.92</t>
+          <t>3.2</t>
         </is>
       </c>
       <c r="AO104" t="inlineStr">
         <is>
-          <t>34.4</t>
+          <t>26.6</t>
         </is>
       </c>
       <c r="AP104" t="inlineStr">
         <is>
-          <t>87.22</t>
+          <t>85.2</t>
         </is>
       </c>
       <c r="AQ104" t="inlineStr">
         <is>
-          <t>97.9501</t>
+          <t>97.8732</t>
         </is>
       </c>
       <c r="AR104" t="inlineStr">
         <is>
-          <t>0.3222</t>
+          <t>0.331</t>
         </is>
       </c>
       <c r="AS104" t="inlineStr">
         <is>
-          <t>0.1015</t>
+          <t>0.098</t>
         </is>
       </c>
       <c r="AT104" t="inlineStr">
         <is>
-          <t>0.26</t>
+          <t>0.304</t>
         </is>
       </c>
       <c r="AU104" t="inlineStr">
         <is>
-          <t>69.16</t>
+          <t>69.3</t>
         </is>
       </c>
       <c r="AV104" t="inlineStr">
         <is>
-          <t>5.6</t>
+          <t>5.7</t>
         </is>
       </c>
       <c r="AW104" t="inlineStr">
         <is>
-          <t>42.33</t>
+          <t>25.0</t>
         </is>
       </c>
       <c r="AX104" t="inlineStr">
         <is>
-          <t>18.41</t>
+          <t>21.9</t>
         </is>
       </c>
       <c r="AY104" t="inlineStr">
         <is>
-          <t>7.0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AZ104" t="inlineStr">
         <is>
-          <t>0.1211</t>
+          <t>0.012</t>
         </is>
       </c>
       <c r="BA104" t="inlineStr">
         <is>
-          <t>8.95</t>
+          <t>9.47</t>
         </is>
       </c>
       <c r="BB104" t="inlineStr">
         <is>
-          <t>44.7</t>
+          <t>40.77</t>
         </is>
       </c>
       <c r="BC104" t="inlineStr">
         <is>
-          <t>90.52</t>
+          <t>90.58</t>
         </is>
       </c>
       <c r="BD104" t="inlineStr">
         <is>
-          <t>0.3945</t>
+          <t>0.4356</t>
         </is>
       </c>
       <c r="BE104" t="inlineStr">
         <is>
-          <t>0.1644</t>
+          <t>0.173</t>
         </is>
       </c>
       <c r="BF104" t="inlineStr">
         <is>
-          <t>29.74</t>
+          <t>27.63</t>
         </is>
       </c>
       <c r="BG104" t="inlineStr">
         <is>
-          <t>In From CF</t>
+          <t>Out To CF</t>
         </is>
       </c>
       <c r="BH104" t="inlineStr">
         <is>
-          <t>77</t>
+          <t>65</t>
         </is>
       </c>
       <c r="BI104" t="inlineStr">
         <is>
-          <t>Rate Field</t>
+          <t>Oracle Park</t>
         </is>
       </c>
       <c r="BJ104" t="inlineStr"/>
@@ -29555,47 +29555,47 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>701852</t>
+          <t>671976</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Drew Cavanaugh</t>
+          <t>Tristan Peters</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>SF</t>
+          <t>CWS</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>CIN</t>
+          <t>TEX</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>2026-08-26T01:45:00Z</t>
+          <t>2026-08-25T23:40:00Z</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="I105" t="inlineStr">
         <is>
-          <t>Brady Singer</t>
+          <t>Jacob deGrom</t>
         </is>
       </c>
       <c r="J105" t="inlineStr">
         <is>
-          <t>663903</t>
+          <t>594798</t>
         </is>
       </c>
       <c r="K105" t="inlineStr">
@@ -29604,7 +29604,7 @@
         </is>
       </c>
       <c r="L105" t="n">
-        <v>42.8</v>
+        <v>42.6</v>
       </c>
       <c r="M105" t="inlineStr">
         <is>
@@ -29618,26 +29618,26 @@
       </c>
       <c r="O105" t="inlineStr">
         <is>
-          <t>Platoon Edge</t>
+          <t>Platoon Edge, Hot Hitter/Streak</t>
         </is>
       </c>
       <c r="P105" t="n">
-        <v>7</v>
+        <v>13.4</v>
       </c>
       <c r="Q105" t="n">
-        <v>51.7</v>
+        <v>50.2</v>
       </c>
       <c r="R105" t="n">
-        <v>55.8</v>
+        <v>40.6</v>
       </c>
       <c r="S105" t="n">
-        <v>86.40000000000001</v>
+        <v>64.3</v>
       </c>
       <c r="T105" t="n">
         <v>80</v>
       </c>
       <c r="U105" t="n">
-        <v>9.300000000000001</v>
+        <v>76.09999999999999</v>
       </c>
       <c r="V105" t="inlineStr">
         <is>
@@ -29651,7 +29651,7 @@
       </c>
       <c r="X105" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="Y105" t="inlineStr">
@@ -29672,7 +29672,7 @@
       <c r="AB105" t="inlineStr"/>
       <c r="AC105" t="inlineStr">
         <is>
-          <t>H:2026 P:2026/2025</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD105" t="inlineStr"/>
@@ -29689,27 +29689,27 @@
       </c>
       <c r="AH105" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AI105" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>23</t>
         </is>
       </c>
       <c r="AJ105" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AK105" t="inlineStr">
         <is>
-          <t>Last 7 games: 4/22, 0 HR</t>
+          <t>Hot streak: 3 HR in last 7 games</t>
         </is>
       </c>
       <c r="AL105" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 9.5% barrel, 23.2 HR allowed</t>
+          <t>platoon edge; pitcher baseline 8.9% barrel, 19.7 HR allowed</t>
         </is>
       </c>
       <c r="AM105" t="inlineStr">
@@ -29719,112 +29719,112 @@
       </c>
       <c r="AN105" t="inlineStr">
         <is>
-          <t>3.2</t>
+          <t>3.92</t>
         </is>
       </c>
       <c r="AO105" t="inlineStr">
         <is>
-          <t>26.6</t>
+          <t>34.4</t>
         </is>
       </c>
       <c r="AP105" t="inlineStr">
         <is>
-          <t>85.2</t>
+          <t>87.22</t>
         </is>
       </c>
       <c r="AQ105" t="inlineStr">
         <is>
-          <t>97.8732</t>
+          <t>97.9501</t>
         </is>
       </c>
       <c r="AR105" t="inlineStr">
         <is>
-          <t>0.331</t>
+          <t>0.3222</t>
         </is>
       </c>
       <c r="AS105" t="inlineStr">
         <is>
-          <t>0.098</t>
+          <t>0.1015</t>
         </is>
       </c>
       <c r="AT105" t="inlineStr">
         <is>
-          <t>0.304</t>
+          <t>0.26</t>
         </is>
       </c>
       <c r="AU105" t="inlineStr">
         <is>
-          <t>69.3</t>
+          <t>69.16</t>
         </is>
       </c>
       <c r="AV105" t="inlineStr">
         <is>
-          <t>5.7</t>
+          <t>5.6</t>
         </is>
       </c>
       <c r="AW105" t="inlineStr">
         <is>
-          <t>25.0</t>
+          <t>42.33</t>
         </is>
       </c>
       <c r="AX105" t="inlineStr">
         <is>
-          <t>21.9</t>
+          <t>18.41</t>
         </is>
       </c>
       <c r="AY105" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>7.0</t>
         </is>
       </c>
       <c r="AZ105" t="inlineStr">
         <is>
-          <t>0.012</t>
+          <t>0.1211</t>
         </is>
       </c>
       <c r="BA105" t="inlineStr">
         <is>
-          <t>9.47</t>
+          <t>8.95</t>
         </is>
       </c>
       <c r="BB105" t="inlineStr">
         <is>
-          <t>40.77</t>
+          <t>44.7</t>
         </is>
       </c>
       <c r="BC105" t="inlineStr">
         <is>
-          <t>90.58</t>
+          <t>90.52</t>
         </is>
       </c>
       <c r="BD105" t="inlineStr">
         <is>
-          <t>0.4356</t>
+          <t>0.3945</t>
         </is>
       </c>
       <c r="BE105" t="inlineStr">
         <is>
-          <t>0.173</t>
+          <t>0.1644</t>
         </is>
       </c>
       <c r="BF105" t="inlineStr">
         <is>
-          <t>27.63</t>
+          <t>29.74</t>
         </is>
       </c>
       <c r="BG105" t="inlineStr">
         <is>
-          <t>Out To CF</t>
+          <t>In From CF</t>
         </is>
       </c>
       <c r="BH105" t="inlineStr">
         <is>
-          <t>65</t>
+          <t>78</t>
         </is>
       </c>
       <c r="BI105" t="inlineStr">
         <is>
-          <t>Oracle Park</t>
+          <t>Rate Field</t>
         </is>
       </c>
       <c r="BJ105" t="inlineStr"/>
@@ -34863,47 +34863,47 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>686668</t>
+          <t>663968</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Brenton Doyle</t>
+          <t>Jake Mangum</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>CWS</t>
+          <t>PIT</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>TEX</t>
+          <t>SD</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>2026-08-25T23:40:00Z</t>
+          <t>2026-08-26T01:40:00Z</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Warmup</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I124" t="inlineStr">
         <is>
-          <t>Jacob deGrom</t>
+          <t>Michael King</t>
         </is>
       </c>
       <c r="J124" t="inlineStr">
         <is>
-          <t>594798</t>
+          <t>650633</t>
         </is>
       </c>
       <c r="K124" t="inlineStr">
@@ -34926,26 +34926,26 @@
       </c>
       <c r="O124" t="inlineStr">
         <is>
-          <t>No major boost</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P124" t="n">
-        <v>24</v>
+        <v>6.3</v>
       </c>
       <c r="Q124" t="n">
-        <v>50.2</v>
+        <v>39.3</v>
       </c>
       <c r="R124" t="n">
-        <v>42.1</v>
+        <v>59.6</v>
       </c>
       <c r="S124" t="n">
-        <v>52.4</v>
+        <v>76.2</v>
       </c>
       <c r="T124" t="n">
-        <v>50</v>
+        <v>75</v>
       </c>
       <c r="U124" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="V124" t="inlineStr">
         <is>
@@ -34959,7 +34959,7 @@
       </c>
       <c r="X124" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>6</t>
         </is>
       </c>
       <c r="Y124" t="inlineStr">
@@ -34997,27 +34997,27 @@
       </c>
       <c r="AH124" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AI124" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="AJ124" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="AI124" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="AJ124" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="AK124" t="inlineStr">
         <is>
-          <t>Last 7 games: 0/10, 0 HR</t>
+          <t>Last 7 games: 3/20, 0 HR</t>
         </is>
       </c>
       <c r="AL124" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 8.9% barrel, 19.7 HR allowed</t>
+          <t>switch hitter; pitcher baseline 9.4% barrel, 16.2 HR allowed</t>
         </is>
       </c>
       <c r="AM124" t="inlineStr">
@@ -35027,112 +35027,112 @@
       </c>
       <c r="AN124" t="inlineStr">
         <is>
-          <t>7.4</t>
+          <t>2.28</t>
         </is>
       </c>
       <c r="AO124" t="inlineStr">
         <is>
-          <t>36.27</t>
+          <t>29.41</t>
         </is>
       </c>
       <c r="AP124" t="inlineStr">
         <is>
-          <t>88.5</t>
+          <t>85.9</t>
         </is>
       </c>
       <c r="AQ124" t="inlineStr">
         <is>
-          <t>99.2931</t>
+          <t>96.7083</t>
         </is>
       </c>
       <c r="AR124" t="inlineStr">
         <is>
-          <t>0.3184</t>
+          <t>0.3325</t>
         </is>
       </c>
       <c r="AS124" t="inlineStr">
         <is>
-          <t>0.1098</t>
+          <t>0.0822</t>
         </is>
       </c>
       <c r="AT124" t="inlineStr">
         <is>
-          <t>0.258</t>
+          <t>0.283</t>
         </is>
       </c>
       <c r="AU124" t="inlineStr">
         <is>
-          <t>71.68</t>
+          <t>67.58</t>
         </is>
       </c>
       <c r="AV124" t="inlineStr">
         <is>
-          <t>12.57</t>
+          <t>4.01</t>
         </is>
       </c>
       <c r="AW124" t="inlineStr">
         <is>
-          <t>37.55</t>
+          <t>27.51</t>
         </is>
       </c>
       <c r="AX124" t="inlineStr">
         <is>
-          <t>25.27</t>
+          <t>15.56</t>
         </is>
       </c>
       <c r="AY124" t="inlineStr">
         <is>
-          <t>5.9</t>
+          <t>3.7</t>
         </is>
       </c>
       <c r="AZ124" t="inlineStr">
         <is>
-          <t>0.0975</t>
+          <t>0.0846</t>
         </is>
       </c>
       <c r="BA124" t="inlineStr">
         <is>
-          <t>8.95</t>
+          <t>9.37</t>
         </is>
       </c>
       <c r="BB124" t="inlineStr">
         <is>
-          <t>44.7</t>
+          <t>34.11</t>
         </is>
       </c>
       <c r="BC124" t="inlineStr">
         <is>
-          <t>90.52</t>
+          <t>87.31</t>
         </is>
       </c>
       <c r="BD124" t="inlineStr">
         <is>
-          <t>0.3945</t>
+          <t>0.4095</t>
         </is>
       </c>
       <c r="BE124" t="inlineStr">
         <is>
-          <t>0.1644</t>
+          <t>0.173</t>
         </is>
       </c>
       <c r="BF124" t="inlineStr">
         <is>
-          <t>29.74</t>
+          <t>27.82</t>
         </is>
       </c>
       <c r="BG124" t="inlineStr">
         <is>
-          <t>In From CF</t>
+          <t>Out To RF</t>
         </is>
       </c>
       <c r="BH124" t="inlineStr">
         <is>
-          <t>77</t>
+          <t>80</t>
         </is>
       </c>
       <c r="BI124" t="inlineStr">
         <is>
-          <t>Rate Field</t>
+          <t>Petco Park</t>
         </is>
       </c>
       <c r="BJ124" t="inlineStr"/>
@@ -35143,47 +35143,47 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>663968</t>
+          <t>686668</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Jake Mangum</t>
+          <t>Brenton Doyle</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>PIT</t>
+          <t>CWS</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>SD</t>
+          <t>TEX</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>2026-08-26T01:40:00Z</t>
+          <t>2026-08-25T23:40:00Z</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I125" t="inlineStr">
         <is>
-          <t>Michael King</t>
+          <t>Jacob deGrom</t>
         </is>
       </c>
       <c r="J125" t="inlineStr">
         <is>
-          <t>650633</t>
+          <t>594798</t>
         </is>
       </c>
       <c r="K125" t="inlineStr">
@@ -35192,7 +35192,7 @@
         </is>
       </c>
       <c r="L125" t="n">
-        <v>38.1</v>
+        <v>37.9</v>
       </c>
       <c r="M125" t="inlineStr">
         <is>
@@ -35206,26 +35206,26 @@
       </c>
       <c r="O125" t="inlineStr">
         <is>
-          <t>Platoon Edge</t>
+          <t>No major boost</t>
         </is>
       </c>
       <c r="P125" t="n">
-        <v>6.3</v>
+        <v>24</v>
       </c>
       <c r="Q125" t="n">
-        <v>39.3</v>
+        <v>50.2</v>
       </c>
       <c r="R125" t="n">
-        <v>59.6</v>
+        <v>40.6</v>
       </c>
       <c r="S125" t="n">
-        <v>76.2</v>
+        <v>52.4</v>
       </c>
       <c r="T125" t="n">
-        <v>75</v>
+        <v>50</v>
       </c>
       <c r="U125" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="V125" t="inlineStr">
         <is>
@@ -35239,7 +35239,7 @@
       </c>
       <c r="X125" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>8</t>
         </is>
       </c>
       <c r="Y125" t="inlineStr">
@@ -35277,12 +35277,12 @@
       </c>
       <c r="AH125" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AI125" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>10</t>
         </is>
       </c>
       <c r="AJ125" t="inlineStr">
@@ -35292,12 +35292,12 @@
       </c>
       <c r="AK125" t="inlineStr">
         <is>
-          <t>Last 7 games: 3/20, 0 HR</t>
+          <t>Last 7 games: 0/10, 0 HR</t>
         </is>
       </c>
       <c r="AL125" t="inlineStr">
         <is>
-          <t>switch hitter; pitcher baseline 9.4% barrel, 16.2 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 8.9% barrel, 19.7 HR allowed</t>
         </is>
       </c>
       <c r="AM125" t="inlineStr">
@@ -35307,112 +35307,112 @@
       </c>
       <c r="AN125" t="inlineStr">
         <is>
-          <t>2.28</t>
+          <t>7.4</t>
         </is>
       </c>
       <c r="AO125" t="inlineStr">
         <is>
-          <t>29.41</t>
+          <t>36.27</t>
         </is>
       </c>
       <c r="AP125" t="inlineStr">
         <is>
-          <t>85.9</t>
+          <t>88.5</t>
         </is>
       </c>
       <c r="AQ125" t="inlineStr">
         <is>
-          <t>96.7083</t>
+          <t>99.2931</t>
         </is>
       </c>
       <c r="AR125" t="inlineStr">
         <is>
-          <t>0.3325</t>
+          <t>0.3184</t>
         </is>
       </c>
       <c r="AS125" t="inlineStr">
         <is>
-          <t>0.0822</t>
+          <t>0.1098</t>
         </is>
       </c>
       <c r="AT125" t="inlineStr">
         <is>
-          <t>0.283</t>
+          <t>0.258</t>
         </is>
       </c>
       <c r="AU125" t="inlineStr">
         <is>
-          <t>67.58</t>
+          <t>71.68</t>
         </is>
       </c>
       <c r="AV125" t="inlineStr">
         <is>
-          <t>4.01</t>
+          <t>12.57</t>
         </is>
       </c>
       <c r="AW125" t="inlineStr">
         <is>
-          <t>27.51</t>
+          <t>37.55</t>
         </is>
       </c>
       <c r="AX125" t="inlineStr">
         <is>
-          <t>15.56</t>
+          <t>25.27</t>
         </is>
       </c>
       <c r="AY125" t="inlineStr">
         <is>
-          <t>3.7</t>
+          <t>5.9</t>
         </is>
       </c>
       <c r="AZ125" t="inlineStr">
         <is>
-          <t>0.0846</t>
+          <t>0.0975</t>
         </is>
       </c>
       <c r="BA125" t="inlineStr">
         <is>
-          <t>9.37</t>
+          <t>8.95</t>
         </is>
       </c>
       <c r="BB125" t="inlineStr">
         <is>
-          <t>34.11</t>
+          <t>44.7</t>
         </is>
       </c>
       <c r="BC125" t="inlineStr">
         <is>
-          <t>87.31</t>
+          <t>90.52</t>
         </is>
       </c>
       <c r="BD125" t="inlineStr">
         <is>
-          <t>0.4095</t>
+          <t>0.3945</t>
         </is>
       </c>
       <c r="BE125" t="inlineStr">
         <is>
-          <t>0.173</t>
+          <t>0.1644</t>
         </is>
       </c>
       <c r="BF125" t="inlineStr">
         <is>
-          <t>27.82</t>
+          <t>29.74</t>
         </is>
       </c>
       <c r="BG125" t="inlineStr">
         <is>
-          <t>Out To RF</t>
+          <t>In From CF</t>
         </is>
       </c>
       <c r="BH125" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>78</t>
         </is>
       </c>
       <c r="BI125" t="inlineStr">
         <is>
-          <t>Petco Park</t>
+          <t>Rate Field</t>
         </is>
       </c>
       <c r="BJ125" t="inlineStr"/>
@@ -35472,7 +35472,7 @@
         </is>
       </c>
       <c r="L126" t="n">
-        <v>37.9</v>
+        <v>37.7</v>
       </c>
       <c r="M126" t="inlineStr">
         <is>
@@ -35496,7 +35496,7 @@
         <v>50.2</v>
       </c>
       <c r="R126" t="n">
-        <v>42.1</v>
+        <v>40.6</v>
       </c>
       <c r="S126" t="n">
         <v>76.2</v>
@@ -35687,7 +35687,7 @@
       </c>
       <c r="BH126" t="inlineStr">
         <is>
-          <t>77</t>
+          <t>78</t>
         </is>
       </c>
       <c r="BI126" t="inlineStr">
@@ -37103,32 +37103,32 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>691011</t>
+          <t>670770</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Drew Romo</t>
+          <t>TJ Friedl</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>CWS</t>
+          <t>CIN</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>TEX</t>
+          <t>SF</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>2026-08-25T23:40:00Z</t>
+          <t>2026-08-26T01:45:00Z</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Warmup</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
@@ -37138,12 +37138,12 @@
       </c>
       <c r="I132" t="inlineStr">
         <is>
-          <t>Jacob deGrom</t>
+          <t>Adrian Houser</t>
         </is>
       </c>
       <c r="J132" t="inlineStr">
         <is>
-          <t>594798</t>
+          <t>605288</t>
         </is>
       </c>
       <c r="K132" t="inlineStr">
@@ -37152,7 +37152,7 @@
         </is>
       </c>
       <c r="L132" t="n">
-        <v>36</v>
+        <v>35.9</v>
       </c>
       <c r="M132" t="inlineStr">
         <is>
@@ -37170,22 +37170,22 @@
         </is>
       </c>
       <c r="P132" t="n">
-        <v>9.9</v>
+        <v>9.4</v>
       </c>
       <c r="Q132" t="n">
-        <v>48.1</v>
+        <v>45.6</v>
       </c>
       <c r="R132" t="n">
-        <v>42.1</v>
+        <v>55.8</v>
       </c>
       <c r="S132" t="n">
         <v>44.8</v>
       </c>
       <c r="T132" t="n">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="U132" t="n">
-        <v>37.8</v>
+        <v>0</v>
       </c>
       <c r="V132" t="inlineStr">
         <is>
@@ -37237,27 +37237,27 @@
       </c>
       <c r="AH132" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AI132" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>12</t>
         </is>
       </c>
       <c r="AJ132" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK132" t="inlineStr">
         <is>
-          <t>Last 7 games: 4/16, 1 HR</t>
+          <t>Last 7 games: 1/12, 0 HR</t>
         </is>
       </c>
       <c r="AL132" t="inlineStr">
         <is>
-          <t>switch hitter; pitcher baseline 8.9% barrel, 19.7 HR allowed</t>
+          <t>platoon edge; pitcher baseline 8.0% barrel, 13.5 HR allowed</t>
         </is>
       </c>
       <c r="AM132" t="inlineStr">
@@ -37267,112 +37267,112 @@
       </c>
       <c r="AN132" t="inlineStr">
         <is>
-          <t>6.5</t>
+          <t>2.56</t>
         </is>
       </c>
       <c r="AO132" t="inlineStr">
         <is>
-          <t>26.8</t>
+          <t>28.88</t>
         </is>
       </c>
       <c r="AP132" t="inlineStr">
         <is>
-          <t>84.2</t>
+          <t>87.31</t>
         </is>
       </c>
       <c r="AQ132" t="inlineStr">
         <is>
-          <t>95.305</t>
+          <t>97.0031</t>
         </is>
       </c>
       <c r="AR132" t="inlineStr">
         <is>
-          <t>0.2086</t>
+          <t>0.2631</t>
         </is>
       </c>
       <c r="AS132" t="inlineStr">
         <is>
-          <t>0.0777</t>
+          <t>0.0732</t>
         </is>
       </c>
       <c r="AT132" t="inlineStr">
         <is>
-          <t>0.1785</t>
+          <t>0.2531</t>
         </is>
       </c>
       <c r="AU132" t="inlineStr">
         <is>
-          <t>68.49</t>
+          <t>70.67</t>
         </is>
       </c>
       <c r="AV132" t="inlineStr">
         <is>
-          <t>3.78</t>
+          <t>9.54</t>
         </is>
       </c>
       <c r="AW132" t="inlineStr">
         <is>
-          <t>38.2</t>
+          <t>39.53</t>
         </is>
       </c>
       <c r="AX132" t="inlineStr">
         <is>
-          <t>31.7</t>
+          <t>24.89</t>
         </is>
       </c>
       <c r="AY132" t="inlineStr">
         <is>
-          <t>4.9</t>
+          <t>6.3</t>
         </is>
       </c>
       <c r="AZ132" t="inlineStr">
         <is>
-          <t>0.112</t>
+          <t>0.089</t>
         </is>
       </c>
       <c r="BA132" t="inlineStr">
         <is>
-          <t>8.95</t>
+          <t>7.99</t>
         </is>
       </c>
       <c r="BB132" t="inlineStr">
         <is>
-          <t>44.7</t>
+          <t>43.82</t>
         </is>
       </c>
       <c r="BC132" t="inlineStr">
         <is>
-          <t>90.52</t>
+          <t>89.92</t>
         </is>
       </c>
       <c r="BD132" t="inlineStr">
         <is>
-          <t>0.3945</t>
+          <t>0.4353</t>
         </is>
       </c>
       <c r="BE132" t="inlineStr">
         <is>
-          <t>0.1644</t>
+          <t>0.1708</t>
         </is>
       </c>
       <c r="BF132" t="inlineStr">
         <is>
-          <t>29.74</t>
+          <t>23.46</t>
         </is>
       </c>
       <c r="BG132" t="inlineStr">
         <is>
-          <t>In From CF</t>
+          <t>Out To CF</t>
         </is>
       </c>
       <c r="BH132" t="inlineStr">
         <is>
-          <t>77</t>
+          <t>65</t>
         </is>
       </c>
       <c r="BI132" t="inlineStr">
         <is>
-          <t>Rate Field</t>
+          <t>Oracle Park</t>
         </is>
       </c>
       <c r="BJ132" t="inlineStr"/>
@@ -37383,32 +37383,32 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>670770</t>
+          <t>691011</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>TJ Friedl</t>
+          <t>Drew Romo</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>CIN</t>
+          <t>CWS</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>SF</t>
+          <t>TEX</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>2026-08-26T01:45:00Z</t>
+          <t>2026-08-25T23:40:00Z</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
@@ -37418,12 +37418,12 @@
       </c>
       <c r="I133" t="inlineStr">
         <is>
-          <t>Adrian Houser</t>
+          <t>Jacob deGrom</t>
         </is>
       </c>
       <c r="J133" t="inlineStr">
         <is>
-          <t>605288</t>
+          <t>594798</t>
         </is>
       </c>
       <c r="K133" t="inlineStr">
@@ -37432,7 +37432,7 @@
         </is>
       </c>
       <c r="L133" t="n">
-        <v>35.9</v>
+        <v>35.8</v>
       </c>
       <c r="M133" t="inlineStr">
         <is>
@@ -37450,22 +37450,22 @@
         </is>
       </c>
       <c r="P133" t="n">
-        <v>9.4</v>
+        <v>9.9</v>
       </c>
       <c r="Q133" t="n">
-        <v>45.6</v>
+        <v>48.1</v>
       </c>
       <c r="R133" t="n">
-        <v>55.8</v>
+        <v>40.6</v>
       </c>
       <c r="S133" t="n">
         <v>44.8</v>
       </c>
       <c r="T133" t="n">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="U133" t="n">
-        <v>0</v>
+        <v>37.8</v>
       </c>
       <c r="V133" t="inlineStr">
         <is>
@@ -37517,27 +37517,27 @@
       </c>
       <c r="AH133" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AI133" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="AJ133" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AI133" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="AJ133" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="AK133" t="inlineStr">
         <is>
-          <t>Last 7 games: 1/12, 0 HR</t>
+          <t>Last 7 games: 4/16, 1 HR</t>
         </is>
       </c>
       <c r="AL133" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 8.0% barrel, 13.5 HR allowed</t>
+          <t>switch hitter; pitcher baseline 8.9% barrel, 19.7 HR allowed</t>
         </is>
       </c>
       <c r="AM133" t="inlineStr">
@@ -37547,112 +37547,112 @@
       </c>
       <c r="AN133" t="inlineStr">
         <is>
-          <t>2.56</t>
+          <t>6.5</t>
         </is>
       </c>
       <c r="AO133" t="inlineStr">
         <is>
-          <t>28.88</t>
+          <t>26.8</t>
         </is>
       </c>
       <c r="AP133" t="inlineStr">
         <is>
-          <t>87.31</t>
+          <t>84.2</t>
         </is>
       </c>
       <c r="AQ133" t="inlineStr">
         <is>
-          <t>97.0031</t>
+          <t>95.305</t>
         </is>
       </c>
       <c r="AR133" t="inlineStr">
         <is>
-          <t>0.2631</t>
+          <t>0.2086</t>
         </is>
       </c>
       <c r="AS133" t="inlineStr">
         <is>
-          <t>0.0732</t>
+          <t>0.0777</t>
         </is>
       </c>
       <c r="AT133" t="inlineStr">
         <is>
-          <t>0.2531</t>
+          <t>0.1785</t>
         </is>
       </c>
       <c r="AU133" t="inlineStr">
         <is>
-          <t>70.67</t>
+          <t>68.49</t>
         </is>
       </c>
       <c r="AV133" t="inlineStr">
         <is>
-          <t>9.54</t>
+          <t>3.78</t>
         </is>
       </c>
       <c r="AW133" t="inlineStr">
         <is>
-          <t>39.53</t>
+          <t>38.2</t>
         </is>
       </c>
       <c r="AX133" t="inlineStr">
         <is>
-          <t>24.89</t>
+          <t>31.7</t>
         </is>
       </c>
       <c r="AY133" t="inlineStr">
         <is>
-          <t>6.3</t>
+          <t>4.9</t>
         </is>
       </c>
       <c r="AZ133" t="inlineStr">
         <is>
-          <t>0.089</t>
+          <t>0.112</t>
         </is>
       </c>
       <c r="BA133" t="inlineStr">
         <is>
-          <t>7.99</t>
+          <t>8.95</t>
         </is>
       </c>
       <c r="BB133" t="inlineStr">
         <is>
-          <t>43.82</t>
+          <t>44.7</t>
         </is>
       </c>
       <c r="BC133" t="inlineStr">
         <is>
-          <t>89.92</t>
+          <t>90.52</t>
         </is>
       </c>
       <c r="BD133" t="inlineStr">
         <is>
-          <t>0.4353</t>
+          <t>0.3945</t>
         </is>
       </c>
       <c r="BE133" t="inlineStr">
         <is>
-          <t>0.1708</t>
+          <t>0.1644</t>
         </is>
       </c>
       <c r="BF133" t="inlineStr">
         <is>
-          <t>23.46</t>
+          <t>29.74</t>
         </is>
       </c>
       <c r="BG133" t="inlineStr">
         <is>
-          <t>Out To CF</t>
+          <t>In From CF</t>
         </is>
       </c>
       <c r="BH133" t="inlineStr">
         <is>
-          <t>65</t>
+          <t>78</t>
         </is>
       </c>
       <c r="BI133" t="inlineStr">
         <is>
-          <t>Oracle Park</t>
+          <t>Rate Field</t>
         </is>
       </c>
       <c r="BJ133" t="inlineStr"/>
@@ -38223,56 +38223,56 @@
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>643376</t>
+          <t>663538</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Danny Jansen</t>
+          <t>Nico Hoerner</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>TEX</t>
+          <t>CHC</t>
         </is>
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>CWS</t>
+          <t>AZ</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>2026-08-25T23:40:00Z</t>
+          <t>2026-08-26T01:40:00Z</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Warmup</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I136" t="inlineStr">
         <is>
-          <t>Anthony Kay</t>
+          <t>Brandon Pfaadt</t>
         </is>
       </c>
       <c r="J136" t="inlineStr">
         <is>
-          <t>641743</t>
+          <t>694297</t>
         </is>
       </c>
       <c r="K136" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>R</t>
         </is>
       </c>
       <c r="L136" t="n">
-        <v>35.3</v>
+        <v>35.2</v>
       </c>
       <c r="M136" t="inlineStr">
         <is>
@@ -38286,26 +38286,26 @@
       </c>
       <c r="O136" t="inlineStr">
         <is>
-          <t>Platoon Edge</t>
+          <t>No major boost</t>
         </is>
       </c>
       <c r="P136" t="n">
-        <v>19.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="Q136" t="n">
-        <v>38.5</v>
+        <v>40.8</v>
       </c>
       <c r="R136" t="n">
-        <v>42.1</v>
+        <v>41.7</v>
       </c>
       <c r="S136" t="n">
-        <v>44.8</v>
+        <v>76.2</v>
       </c>
       <c r="T136" t="n">
-        <v>78</v>
+        <v>50</v>
       </c>
       <c r="U136" t="n">
-        <v>0</v>
+        <v>26.4</v>
       </c>
       <c r="V136" t="inlineStr">
         <is>
@@ -38319,7 +38319,7 @@
       </c>
       <c r="X136" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>6</t>
         </is>
       </c>
       <c r="Y136" t="inlineStr">
@@ -38340,7 +38340,7 @@
       <c r="AB136" t="inlineStr"/>
       <c r="AC136" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD136" t="inlineStr"/>
@@ -38357,12 +38357,12 @@
       </c>
       <c r="AH136" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AI136" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>27</t>
         </is>
       </c>
       <c r="AJ136" t="inlineStr">
@@ -38372,12 +38372,12 @@
       </c>
       <c r="AK136" t="inlineStr">
         <is>
-          <t>Last 7 games: 1/15, 0 HR</t>
+          <t>Last 7 games: 8/27, 0 HR</t>
         </is>
       </c>
       <c r="AL136" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 8.2% barrel, 16.0 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 8.3% barrel, 15.5 HR allowed</t>
         </is>
       </c>
       <c r="AM136" t="inlineStr">
@@ -38387,112 +38387,112 @@
       </c>
       <c r="AN136" t="inlineStr">
         <is>
-          <t>6.56</t>
+          <t>1.49</t>
         </is>
       </c>
       <c r="AO136" t="inlineStr">
         <is>
-          <t>33.75</t>
+          <t>28.62</t>
         </is>
       </c>
       <c r="AP136" t="inlineStr">
         <is>
-          <t>87.11</t>
+          <t>86.14</t>
         </is>
       </c>
       <c r="AQ136" t="inlineStr">
         <is>
-          <t>97.4711</t>
+          <t>96.2188</t>
         </is>
       </c>
       <c r="AR136" t="inlineStr">
         <is>
-          <t>0.2888</t>
+          <t>0.3784</t>
         </is>
       </c>
       <c r="AS136" t="inlineStr">
         <is>
-          <t>0.1164</t>
+          <t>0.0815</t>
         </is>
       </c>
       <c r="AT136" t="inlineStr">
         <is>
-          <t>0.2598</t>
+          <t>0.3234</t>
         </is>
       </c>
       <c r="AU136" t="inlineStr">
         <is>
-          <t>70.06</t>
+          <t>68.33</t>
         </is>
       </c>
       <c r="AV136" t="inlineStr">
         <is>
-          <t>7.02</t>
+          <t>1.76</t>
         </is>
       </c>
       <c r="AW136" t="inlineStr">
         <is>
-          <t>54.75</t>
+          <t>32.87</t>
         </is>
       </c>
       <c r="AX136" t="inlineStr">
         <is>
-          <t>28.56</t>
+          <t>21.42</t>
         </is>
       </c>
       <c r="AY136" t="inlineStr">
         <is>
-          <t>6.3</t>
+          <t>7.0</t>
         </is>
       </c>
       <c r="AZ136" t="inlineStr">
         <is>
-          <t>0.1455</t>
+          <t>0.097</t>
         </is>
       </c>
       <c r="BA136" t="inlineStr">
         <is>
-          <t>8.2</t>
+          <t>8.31</t>
         </is>
       </c>
       <c r="BB136" t="inlineStr">
         <is>
-          <t>39.7</t>
+          <t>38.24</t>
         </is>
       </c>
       <c r="BC136" t="inlineStr">
         <is>
-          <t>88.4</t>
+          <t>89.19</t>
         </is>
       </c>
       <c r="BD136" t="inlineStr">
         <is>
-          <t>0.404</t>
+          <t>0.4107</t>
         </is>
       </c>
       <c r="BE136" t="inlineStr">
         <is>
-          <t>0.144</t>
+          <t>0.1603</t>
         </is>
       </c>
       <c r="BF136" t="inlineStr">
         <is>
-          <t>21.8</t>
+          <t>22.71</t>
         </is>
       </c>
       <c r="BG136" t="inlineStr">
         <is>
-          <t>In From CF</t>
+          <t>None</t>
         </is>
       </c>
       <c r="BH136" t="inlineStr">
         <is>
-          <t>77</t>
+          <t>72</t>
         </is>
       </c>
       <c r="BI136" t="inlineStr">
         <is>
-          <t>Rate Field</t>
+          <t>Chase Field</t>
         </is>
       </c>
       <c r="BJ136" t="inlineStr"/>
@@ -38503,56 +38503,56 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>663538</t>
+          <t>643376</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Nico Hoerner</t>
+          <t>Danny Jansen</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>CHC</t>
+          <t>TEX</t>
         </is>
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>AZ</t>
+          <t>CWS</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>2026-08-26T01:40:00Z</t>
+          <t>2026-08-25T23:40:00Z</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>9</t>
         </is>
       </c>
       <c r="I137" t="inlineStr">
         <is>
-          <t>Brandon Pfaadt</t>
+          <t>Anthony Kay</t>
         </is>
       </c>
       <c r="J137" t="inlineStr">
         <is>
-          <t>694297</t>
+          <t>641743</t>
         </is>
       </c>
       <c r="K137" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>L</t>
         </is>
       </c>
       <c r="L137" t="n">
-        <v>35.2</v>
+        <v>35.1</v>
       </c>
       <c r="M137" t="inlineStr">
         <is>
@@ -38566,26 +38566,26 @@
       </c>
       <c r="O137" t="inlineStr">
         <is>
-          <t>No major boost</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P137" t="n">
-        <v>8.199999999999999</v>
+        <v>19.6</v>
       </c>
       <c r="Q137" t="n">
-        <v>40.8</v>
+        <v>38.5</v>
       </c>
       <c r="R137" t="n">
-        <v>41.7</v>
+        <v>40.6</v>
       </c>
       <c r="S137" t="n">
-        <v>76.2</v>
+        <v>44.8</v>
       </c>
       <c r="T137" t="n">
-        <v>50</v>
+        <v>78</v>
       </c>
       <c r="U137" t="n">
-        <v>26.4</v>
+        <v>0</v>
       </c>
       <c r="V137" t="inlineStr">
         <is>
@@ -38599,7 +38599,7 @@
       </c>
       <c r="X137" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>9</t>
         </is>
       </c>
       <c r="Y137" t="inlineStr">
@@ -38620,7 +38620,7 @@
       <c r="AB137" t="inlineStr"/>
       <c r="AC137" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026/2025</t>
+          <t>H:2026/2025 P:2026</t>
         </is>
       </c>
       <c r="AD137" t="inlineStr"/>
@@ -38637,12 +38637,12 @@
       </c>
       <c r="AH137" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AI137" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>15</t>
         </is>
       </c>
       <c r="AJ137" t="inlineStr">
@@ -38652,12 +38652,12 @@
       </c>
       <c r="AK137" t="inlineStr">
         <is>
-          <t>Last 7 games: 8/27, 0 HR</t>
+          <t>Last 7 games: 1/15, 0 HR</t>
         </is>
       </c>
       <c r="AL137" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 8.3% barrel, 15.5 HR allowed</t>
+          <t>platoon edge; pitcher baseline 8.2% barrel, 16.0 HR allowed</t>
         </is>
       </c>
       <c r="AM137" t="inlineStr">
@@ -38667,112 +38667,112 @@
       </c>
       <c r="AN137" t="inlineStr">
         <is>
-          <t>1.49</t>
+          <t>6.56</t>
         </is>
       </c>
       <c r="AO137" t="inlineStr">
         <is>
-          <t>28.62</t>
+          <t>33.75</t>
         </is>
       </c>
       <c r="AP137" t="inlineStr">
         <is>
-          <t>86.14</t>
+          <t>87.11</t>
         </is>
       </c>
       <c r="AQ137" t="inlineStr">
         <is>
-          <t>96.2188</t>
+          <t>97.4711</t>
         </is>
       </c>
       <c r="AR137" t="inlineStr">
         <is>
-          <t>0.3784</t>
+          <t>0.2888</t>
         </is>
       </c>
       <c r="AS137" t="inlineStr">
         <is>
-          <t>0.0815</t>
+          <t>0.1164</t>
         </is>
       </c>
       <c r="AT137" t="inlineStr">
         <is>
-          <t>0.3234</t>
+          <t>0.2598</t>
         </is>
       </c>
       <c r="AU137" t="inlineStr">
         <is>
-          <t>68.33</t>
+          <t>70.06</t>
         </is>
       </c>
       <c r="AV137" t="inlineStr">
         <is>
-          <t>1.76</t>
+          <t>7.02</t>
         </is>
       </c>
       <c r="AW137" t="inlineStr">
         <is>
-          <t>32.87</t>
+          <t>54.75</t>
         </is>
       </c>
       <c r="AX137" t="inlineStr">
         <is>
-          <t>21.42</t>
+          <t>28.56</t>
         </is>
       </c>
       <c r="AY137" t="inlineStr">
         <is>
-          <t>7.0</t>
+          <t>6.3</t>
         </is>
       </c>
       <c r="AZ137" t="inlineStr">
         <is>
-          <t>0.097</t>
+          <t>0.1455</t>
         </is>
       </c>
       <c r="BA137" t="inlineStr">
         <is>
-          <t>8.31</t>
+          <t>8.2</t>
         </is>
       </c>
       <c r="BB137" t="inlineStr">
         <is>
-          <t>38.24</t>
+          <t>39.7</t>
         </is>
       </c>
       <c r="BC137" t="inlineStr">
         <is>
-          <t>89.19</t>
+          <t>88.4</t>
         </is>
       </c>
       <c r="BD137" t="inlineStr">
         <is>
-          <t>0.4107</t>
+          <t>0.404</t>
         </is>
       </c>
       <c r="BE137" t="inlineStr">
         <is>
-          <t>0.1603</t>
+          <t>0.144</t>
         </is>
       </c>
       <c r="BF137" t="inlineStr">
         <is>
-          <t>22.71</t>
+          <t>21.8</t>
         </is>
       </c>
       <c r="BG137" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>In From CF</t>
         </is>
       </c>
       <c r="BH137" t="inlineStr">
         <is>
-          <t>72</t>
+          <t>78</t>
         </is>
       </c>
       <c r="BI137" t="inlineStr">
         <is>
-          <t>Chase Field</t>
+          <t>Rate Field</t>
         </is>
       </c>
       <c r="BJ137" t="inlineStr"/>
@@ -39899,56 +39899,56 @@
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>683227</t>
+          <t>687957</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Cody Freeman</t>
+          <t>Dustin Harris</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>TEX</t>
+          <t>SD</t>
         </is>
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>CWS</t>
+          <t>PIT</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>2026-08-25T23:40:00Z</t>
+          <t>2026-08-26T01:40:00Z</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>Warmup</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>9</t>
         </is>
       </c>
       <c r="I142" t="inlineStr">
         <is>
-          <t>Anthony Kay</t>
+          <t>Paul Skenes</t>
         </is>
       </c>
       <c r="J142" t="inlineStr">
         <is>
-          <t>641743</t>
+          <t>694973</t>
         </is>
       </c>
       <c r="K142" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>R</t>
         </is>
       </c>
       <c r="L142" t="n">
-        <v>32.2</v>
+        <v>32.1</v>
       </c>
       <c r="M142" t="inlineStr">
         <is>
@@ -39966,22 +39966,22 @@
         </is>
       </c>
       <c r="P142" t="n">
-        <v>0.8</v>
+        <v>2.6</v>
       </c>
       <c r="Q142" t="n">
-        <v>38.5</v>
+        <v>30.1</v>
       </c>
       <c r="R142" t="n">
-        <v>42.1</v>
+        <v>59.6</v>
       </c>
       <c r="S142" t="n">
-        <v>52.4</v>
+        <v>44.8</v>
       </c>
       <c r="T142" t="n">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="U142" t="n">
-        <v>40.3</v>
+        <v>32</v>
       </c>
       <c r="V142" t="inlineStr">
         <is>
@@ -39995,7 +39995,7 @@
       </c>
       <c r="X142" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>9</t>
         </is>
       </c>
       <c r="Y142" t="inlineStr">
@@ -40016,7 +40016,7 @@
       <c r="AB142" t="inlineStr"/>
       <c r="AC142" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD142" t="inlineStr"/>
@@ -40033,12 +40033,12 @@
       </c>
       <c r="AH142" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AI142" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>24</t>
         </is>
       </c>
       <c r="AJ142" t="inlineStr">
@@ -40048,12 +40048,12 @@
       </c>
       <c r="AK142" t="inlineStr">
         <is>
-          <t>Contact streak: 7/18 over last 7 games</t>
+          <t>Contact streak: 8/24 over last 7 games</t>
         </is>
       </c>
       <c r="AL142" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 8.2% barrel, 16.0 HR allowed</t>
+          <t>platoon edge; pitcher baseline 6.9% barrel, 13.1 HR allowed</t>
         </is>
       </c>
       <c r="AM142" t="inlineStr">
@@ -40063,112 +40063,112 @@
       </c>
       <c r="AN142" t="inlineStr">
         <is>
-          <t>1.26</t>
+          <t>1.11</t>
         </is>
       </c>
       <c r="AO142" t="inlineStr">
         <is>
-          <t>23.56</t>
+          <t>17.78</t>
         </is>
       </c>
       <c r="AP142" t="inlineStr">
         <is>
-          <t>84.27</t>
+          <t>84.73</t>
         </is>
       </c>
       <c r="AQ142" t="inlineStr">
         <is>
-          <t>94.766</t>
+          <t>93.9291</t>
         </is>
       </c>
       <c r="AR142" t="inlineStr">
         <is>
-          <t>0.2553</t>
+          <t>0.3142</t>
         </is>
       </c>
       <c r="AS142" t="inlineStr">
         <is>
-          <t>0.0499</t>
+          <t>0.0715</t>
         </is>
       </c>
       <c r="AT142" t="inlineStr">
         <is>
-          <t>0.2388</t>
+          <t>0.2884</t>
         </is>
       </c>
       <c r="AU142" t="inlineStr">
         <is>
-          <t>66.74</t>
+          <t>66.75</t>
         </is>
       </c>
       <c r="AV142" t="inlineStr">
         <is>
-          <t>0.45</t>
+          <t>2.73</t>
         </is>
       </c>
       <c r="AW142" t="inlineStr">
         <is>
-          <t>45.94</t>
+          <t>49.46</t>
         </is>
       </c>
       <c r="AX142" t="inlineStr">
         <is>
-          <t>16.85</t>
+          <t>24.43</t>
         </is>
       </c>
       <c r="AY142" t="inlineStr">
         <is>
-          <t>0.9</t>
+          <t>0.3</t>
         </is>
       </c>
       <c r="AZ142" t="inlineStr">
         <is>
-          <t>0.0692</t>
+          <t>0.1038</t>
         </is>
       </c>
       <c r="BA142" t="inlineStr">
         <is>
-          <t>8.2</t>
+          <t>6.92</t>
         </is>
       </c>
       <c r="BB142" t="inlineStr">
         <is>
-          <t>39.7</t>
+          <t>39.33</t>
         </is>
       </c>
       <c r="BC142" t="inlineStr">
         <is>
-          <t>88.4</t>
+          <t>88.23</t>
         </is>
       </c>
       <c r="BD142" t="inlineStr">
         <is>
-          <t>0.404</t>
+          <t>0.335</t>
         </is>
       </c>
       <c r="BE142" t="inlineStr">
         <is>
-          <t>0.144</t>
+          <t>0.1253</t>
         </is>
       </c>
       <c r="BF142" t="inlineStr">
         <is>
-          <t>21.8</t>
+          <t>23.99</t>
         </is>
       </c>
       <c r="BG142" t="inlineStr">
         <is>
-          <t>In From CF</t>
+          <t>Out To RF</t>
         </is>
       </c>
       <c r="BH142" t="inlineStr">
         <is>
-          <t>77</t>
+          <t>80</t>
         </is>
       </c>
       <c r="BI142" t="inlineStr">
         <is>
-          <t>Rate Field</t>
+          <t>Petco Park</t>
         </is>
       </c>
       <c r="BJ142" t="inlineStr"/>
@@ -40179,56 +40179,56 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>687957</t>
+          <t>683227</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Dustin Harris</t>
+          <t>Cody Freeman</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>SD</t>
+          <t>TEX</t>
         </is>
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>PIT</t>
+          <t>CWS</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>2026-08-26T01:40:00Z</t>
+          <t>2026-08-25T23:40:00Z</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I143" t="inlineStr">
         <is>
-          <t>Paul Skenes</t>
+          <t>Anthony Kay</t>
         </is>
       </c>
       <c r="J143" t="inlineStr">
         <is>
-          <t>694973</t>
+          <t>641743</t>
         </is>
       </c>
       <c r="K143" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>L</t>
         </is>
       </c>
       <c r="L143" t="n">
-        <v>32.1</v>
+        <v>32</v>
       </c>
       <c r="M143" t="inlineStr">
         <is>
@@ -40246,22 +40246,22 @@
         </is>
       </c>
       <c r="P143" t="n">
-        <v>2.6</v>
+        <v>0.8</v>
       </c>
       <c r="Q143" t="n">
-        <v>30.1</v>
+        <v>38.5</v>
       </c>
       <c r="R143" t="n">
-        <v>59.6</v>
+        <v>40.6</v>
       </c>
       <c r="S143" t="n">
-        <v>44.8</v>
+        <v>52.4</v>
       </c>
       <c r="T143" t="n">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="U143" t="n">
-        <v>32</v>
+        <v>40.3</v>
       </c>
       <c r="V143" t="inlineStr">
         <is>
@@ -40275,7 +40275,7 @@
       </c>
       <c r="X143" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="Y143" t="inlineStr">
@@ -40296,7 +40296,7 @@
       <c r="AB143" t="inlineStr"/>
       <c r="AC143" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026/2025</t>
+          <t>H:2026/2025 P:2026</t>
         </is>
       </c>
       <c r="AD143" t="inlineStr"/>
@@ -40313,12 +40313,12 @@
       </c>
       <c r="AH143" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AI143" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>18</t>
         </is>
       </c>
       <c r="AJ143" t="inlineStr">
@@ -40328,12 +40328,12 @@
       </c>
       <c r="AK143" t="inlineStr">
         <is>
-          <t>Contact streak: 8/24 over last 7 games</t>
+          <t>Contact streak: 7/18 over last 7 games</t>
         </is>
       </c>
       <c r="AL143" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 6.9% barrel, 13.1 HR allowed</t>
+          <t>platoon edge; pitcher baseline 8.2% barrel, 16.0 HR allowed</t>
         </is>
       </c>
       <c r="AM143" t="inlineStr">
@@ -40343,112 +40343,112 @@
       </c>
       <c r="AN143" t="inlineStr">
         <is>
-          <t>1.11</t>
+          <t>1.26</t>
         </is>
       </c>
       <c r="AO143" t="inlineStr">
         <is>
-          <t>17.78</t>
+          <t>23.56</t>
         </is>
       </c>
       <c r="AP143" t="inlineStr">
         <is>
-          <t>84.73</t>
+          <t>84.27</t>
         </is>
       </c>
       <c r="AQ143" t="inlineStr">
         <is>
-          <t>93.9291</t>
+          <t>94.766</t>
         </is>
       </c>
       <c r="AR143" t="inlineStr">
         <is>
-          <t>0.3142</t>
+          <t>0.2553</t>
         </is>
       </c>
       <c r="AS143" t="inlineStr">
         <is>
-          <t>0.0715</t>
+          <t>0.0499</t>
         </is>
       </c>
       <c r="AT143" t="inlineStr">
         <is>
-          <t>0.2884</t>
+          <t>0.2388</t>
         </is>
       </c>
       <c r="AU143" t="inlineStr">
         <is>
-          <t>66.75</t>
+          <t>66.74</t>
         </is>
       </c>
       <c r="AV143" t="inlineStr">
         <is>
-          <t>2.73</t>
+          <t>0.45</t>
         </is>
       </c>
       <c r="AW143" t="inlineStr">
         <is>
-          <t>49.46</t>
+          <t>45.94</t>
         </is>
       </c>
       <c r="AX143" t="inlineStr">
         <is>
-          <t>24.43</t>
+          <t>16.85</t>
         </is>
       </c>
       <c r="AY143" t="inlineStr">
         <is>
-          <t>0.3</t>
+          <t>0.9</t>
         </is>
       </c>
       <c r="AZ143" t="inlineStr">
         <is>
-          <t>0.1038</t>
+          <t>0.0692</t>
         </is>
       </c>
       <c r="BA143" t="inlineStr">
         <is>
-          <t>6.92</t>
+          <t>8.2</t>
         </is>
       </c>
       <c r="BB143" t="inlineStr">
         <is>
-          <t>39.33</t>
+          <t>39.7</t>
         </is>
       </c>
       <c r="BC143" t="inlineStr">
         <is>
-          <t>88.23</t>
+          <t>88.4</t>
         </is>
       </c>
       <c r="BD143" t="inlineStr">
         <is>
-          <t>0.335</t>
+          <t>0.404</t>
         </is>
       </c>
       <c r="BE143" t="inlineStr">
         <is>
-          <t>0.1253</t>
+          <t>0.144</t>
         </is>
       </c>
       <c r="BF143" t="inlineStr">
         <is>
-          <t>23.99</t>
+          <t>21.8</t>
         </is>
       </c>
       <c r="BG143" t="inlineStr">
         <is>
-          <t>Out To RF</t>
+          <t>In From CF</t>
         </is>
       </c>
       <c r="BH143" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>78</t>
         </is>
       </c>
       <c r="BI143" t="inlineStr">
         <is>
-          <t>Petco Park</t>
+          <t>Rate Field</t>
         </is>
       </c>
       <c r="BJ143" t="inlineStr"/>
@@ -41950,7 +41950,7 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>67.2</v>
+        <v>67</v>
       </c>
       <c r="M4" t="inlineStr">
         <is>
@@ -41974,7 +41974,7 @@
         <v>50.2</v>
       </c>
       <c r="R4" t="n">
-        <v>42.1</v>
+        <v>40.6</v>
       </c>
       <c r="S4" t="n">
         <v>100</v>
@@ -42165,7 +42165,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>77</t>
+          <t>78</t>
         </is>
       </c>
       <c r="BI4" t="inlineStr">
@@ -46430,7 +46430,7 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>57.6</v>
+        <v>57.4</v>
       </c>
       <c r="M20" t="inlineStr">
         <is>
@@ -46454,7 +46454,7 @@
         <v>38.5</v>
       </c>
       <c r="R20" t="n">
-        <v>42.1</v>
+        <v>40.6</v>
       </c>
       <c r="S20" t="n">
         <v>100</v>
@@ -46645,7 +46645,7 @@
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>77</t>
+          <t>78</t>
         </is>
       </c>
       <c r="BI20" t="inlineStr">
@@ -46710,7 +46710,7 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>57.6</v>
+        <v>57.3</v>
       </c>
       <c r="M21" t="inlineStr">
         <is>
@@ -46734,7 +46734,7 @@
         <v>50.2</v>
       </c>
       <c r="R21" t="n">
-        <v>42.1</v>
+        <v>40.6</v>
       </c>
       <c r="S21" t="n">
         <v>96.59999999999999</v>
@@ -46925,7 +46925,7 @@
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>77</t>
+          <t>78</t>
         </is>
       </c>
       <c r="BI21" t="inlineStr">
